--- a/summaryWithoutAnyLogs.xlsx
+++ b/summaryWithoutAnyLogs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoLand\rah\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED7AA2B-87BE-4278-821B-8937B76BB94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7759F6-3A93-4627-B0D9-101E440D033F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CC082154-BF88-43CA-BD5F-7A15134C974C}"/>
   </bookViews>
@@ -1662,7 +1662,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1851,6 +1851,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFCFC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2150,7 +2156,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2164,14 +2170,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2182,32 +2193,40 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2583,42 +2602,42 @@
       <c r="B1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="12" t="s">
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="12" t="s">
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="14"/>
-      <c r="Y1" s="24" t="s">
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="19"/>
+      <c r="Y1" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Z1" s="24"/>
-      <c r="AA1" s="24"/>
-      <c r="AB1" s="24"/>
-      <c r="AC1" s="24"/>
-      <c r="AD1" s="24"/>
-      <c r="AE1" s="24"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
     </row>
     <row r="2" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
@@ -2649,7 +2668,7 @@
         <v>67</v>
       </c>
       <c r="K2" s="4"/>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="13" t="s">
         <v>2</v>
       </c>
       <c r="M2" s="4" t="s">
@@ -2711,7 +2730,7 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="20" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="4">
@@ -2732,7 +2751,7 @@
       <c r="I3" s="6">
         <v>0</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="20" t="s">
         <v>44</v>
       </c>
       <c r="K3" s="4">
@@ -2753,7 +2772,7 @@
       <c r="P3" s="6">
         <v>0</v>
       </c>
-      <c r="Q3" s="10" t="s">
+      <c r="Q3" s="20" t="s">
         <v>44</v>
       </c>
       <c r="R3" s="4">
@@ -2774,7 +2793,7 @@
       <c r="W3" s="6">
         <v>0</v>
       </c>
-      <c r="Y3" s="25" t="s">
+      <c r="Y3" s="15" t="s">
         <v>44</v>
       </c>
       <c r="Z3" s="4">
@@ -2800,7 +2819,7 @@
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="10"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="4">
         <v>100</v>
       </c>
@@ -2819,7 +2838,7 @@
       <c r="I4" s="6">
         <v>0</v>
       </c>
-      <c r="J4" s="10"/>
+      <c r="J4" s="20"/>
       <c r="K4" s="4">
         <v>100</v>
       </c>
@@ -2838,7 +2857,7 @@
       <c r="P4" s="6">
         <v>0</v>
       </c>
-      <c r="Q4" s="10"/>
+      <c r="Q4" s="20"/>
       <c r="R4" s="4">
         <v>100</v>
       </c>
@@ -2857,7 +2876,7 @@
       <c r="W4" s="6">
         <v>0</v>
       </c>
-      <c r="Y4" s="25"/>
+      <c r="Y4" s="15"/>
       <c r="Z4" s="4">
         <v>100</v>
       </c>
@@ -2881,7 +2900,7 @@
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="10"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="4">
         <v>200</v>
       </c>
@@ -2900,7 +2919,7 @@
       <c r="I5" s="6">
         <v>0</v>
       </c>
-      <c r="J5" s="10"/>
+      <c r="J5" s="20"/>
       <c r="K5" s="4">
         <v>200</v>
       </c>
@@ -2919,7 +2938,7 @@
       <c r="P5" s="6">
         <v>0</v>
       </c>
-      <c r="Q5" s="10"/>
+      <c r="Q5" s="20"/>
       <c r="R5" s="4">
         <v>200</v>
       </c>
@@ -2938,7 +2957,7 @@
       <c r="W5" s="6">
         <v>0</v>
       </c>
-      <c r="Y5" s="25"/>
+      <c r="Y5" s="15"/>
       <c r="Z5" s="4">
         <v>200</v>
       </c>
@@ -2962,7 +2981,7 @@
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="4">
         <v>500</v>
       </c>
@@ -2981,7 +3000,7 @@
       <c r="I6" s="6">
         <v>0</v>
       </c>
-      <c r="J6" s="10"/>
+      <c r="J6" s="20"/>
       <c r="K6" s="4">
         <v>500</v>
       </c>
@@ -3000,7 +3019,7 @@
       <c r="P6" s="6">
         <v>0</v>
       </c>
-      <c r="Q6" s="10"/>
+      <c r="Q6" s="20"/>
       <c r="R6" s="4">
         <v>500</v>
       </c>
@@ -3019,7 +3038,7 @@
       <c r="W6" s="6">
         <v>0</v>
       </c>
-      <c r="Y6" s="25"/>
+      <c r="Y6" s="15"/>
       <c r="Z6" s="4">
         <v>500</v>
       </c>
@@ -3043,7 +3062,7 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="10"/>
+      <c r="C7" s="20"/>
       <c r="D7" s="4">
         <v>1000</v>
       </c>
@@ -3062,7 +3081,7 @@
       <c r="I7" s="6">
         <v>0</v>
       </c>
-      <c r="J7" s="10"/>
+      <c r="J7" s="20"/>
       <c r="K7" s="4">
         <v>1000</v>
       </c>
@@ -3081,7 +3100,7 @@
       <c r="P7" s="6">
         <v>0</v>
       </c>
-      <c r="Q7" s="10"/>
+      <c r="Q7" s="20"/>
       <c r="R7" s="4">
         <v>1000</v>
       </c>
@@ -3100,7 +3119,7 @@
       <c r="W7" s="6">
         <v>0</v>
       </c>
-      <c r="Y7" s="25"/>
+      <c r="Y7" s="15"/>
       <c r="Z7" s="4">
         <v>1000</v>
       </c>
@@ -3124,7 +3143,7 @@
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="20" t="s">
         <v>45</v>
       </c>
       <c r="D8" s="4">
@@ -3145,7 +3164,7 @@
       <c r="I8" s="6">
         <v>0</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="20" t="s">
         <v>45</v>
       </c>
       <c r="K8" s="4">
@@ -3166,7 +3185,7 @@
       <c r="P8" s="6">
         <v>0</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="Q8" s="20" t="s">
         <v>45</v>
       </c>
       <c r="R8" s="4">
@@ -3187,7 +3206,7 @@
       <c r="W8" s="6">
         <v>0</v>
       </c>
-      <c r="Y8" s="25" t="s">
+      <c r="Y8" s="15" t="s">
         <v>45</v>
       </c>
       <c r="Z8" s="4">
@@ -3213,7 +3232,7 @@
       <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="20"/>
       <c r="D9" s="4">
         <v>100</v>
       </c>
@@ -3232,7 +3251,7 @@
       <c r="I9" s="6">
         <v>0</v>
       </c>
-      <c r="J9" s="10"/>
+      <c r="J9" s="20"/>
       <c r="K9" s="4">
         <v>100</v>
       </c>
@@ -3251,7 +3270,7 @@
       <c r="P9" s="6">
         <v>0</v>
       </c>
-      <c r="Q9" s="10"/>
+      <c r="Q9" s="20"/>
       <c r="R9" s="4">
         <v>100</v>
       </c>
@@ -3270,7 +3289,7 @@
       <c r="W9" s="6">
         <v>0</v>
       </c>
-      <c r="Y9" s="25"/>
+      <c r="Y9" s="15"/>
       <c r="Z9" s="4">
         <v>100</v>
       </c>
@@ -3294,7 +3313,7 @@
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="10"/>
+      <c r="C10" s="20"/>
       <c r="D10" s="4">
         <v>200</v>
       </c>
@@ -3313,7 +3332,7 @@
       <c r="I10" s="6">
         <v>0</v>
       </c>
-      <c r="J10" s="10"/>
+      <c r="J10" s="20"/>
       <c r="K10" s="4">
         <v>200</v>
       </c>
@@ -3332,7 +3351,7 @@
       <c r="P10" s="6">
         <v>0</v>
       </c>
-      <c r="Q10" s="10"/>
+      <c r="Q10" s="20"/>
       <c r="R10" s="4">
         <v>200</v>
       </c>
@@ -3351,7 +3370,7 @@
       <c r="W10" s="6">
         <v>0</v>
       </c>
-      <c r="Y10" s="25"/>
+      <c r="Y10" s="15"/>
       <c r="Z10" s="4">
         <v>200</v>
       </c>
@@ -3375,7 +3394,7 @@
       <c r="B11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="20"/>
       <c r="D11" s="4">
         <v>500</v>
       </c>
@@ -3394,7 +3413,7 @@
       <c r="I11" s="6">
         <v>0</v>
       </c>
-      <c r="J11" s="10"/>
+      <c r="J11" s="20"/>
       <c r="K11" s="4">
         <v>500</v>
       </c>
@@ -3413,7 +3432,7 @@
       <c r="P11" s="6">
         <v>0</v>
       </c>
-      <c r="Q11" s="10"/>
+      <c r="Q11" s="20"/>
       <c r="R11" s="4">
         <v>500</v>
       </c>
@@ -3432,7 +3451,7 @@
       <c r="W11" s="6">
         <v>0</v>
       </c>
-      <c r="Y11" s="25"/>
+      <c r="Y11" s="15"/>
       <c r="Z11" s="4">
         <v>500</v>
       </c>
@@ -3456,7 +3475,7 @@
       <c r="B12" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="10"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="4">
         <v>1000</v>
       </c>
@@ -3475,7 +3494,7 @@
       <c r="I12" s="6">
         <v>0</v>
       </c>
-      <c r="J12" s="10"/>
+      <c r="J12" s="20"/>
       <c r="K12" s="4">
         <v>1000</v>
       </c>
@@ -3494,7 +3513,7 @@
       <c r="P12" s="6">
         <v>0</v>
       </c>
-      <c r="Q12" s="10"/>
+      <c r="Q12" s="20"/>
       <c r="R12" s="4">
         <v>1000</v>
       </c>
@@ -3513,7 +3532,7 @@
       <c r="W12" s="6">
         <v>0</v>
       </c>
-      <c r="Y12" s="25"/>
+      <c r="Y12" s="15"/>
       <c r="Z12" s="4">
         <v>1000</v>
       </c>
@@ -3537,7 +3556,7 @@
       <c r="B13" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="21" t="s">
         <v>46</v>
       </c>
       <c r="D13" s="4">
@@ -3558,28 +3577,28 @@
       <c r="I13" s="6">
         <v>0</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="9">
         <v>50</v>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="9">
         <v>25945</v>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="9">
         <v>1.92</v>
       </c>
-      <c r="N13" s="16">
+      <c r="N13" s="9">
         <v>23.39</v>
       </c>
-      <c r="O13" s="16">
+      <c r="O13" s="9">
         <v>389218</v>
       </c>
-      <c r="P13" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="9" t="s">
+      <c r="P13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R13" s="4">
@@ -3600,7 +3619,7 @@
       <c r="W13" s="6">
         <v>0</v>
       </c>
-      <c r="Y13" s="26" t="s">
+      <c r="Y13" s="14" t="s">
         <v>46</v>
       </c>
       <c r="Z13" s="4">
@@ -3626,7 +3645,7 @@
       <c r="B14" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="20"/>
       <c r="D14" s="4">
         <v>100</v>
       </c>
@@ -3645,26 +3664,26 @@
       <c r="I14" s="6">
         <v>0</v>
       </c>
-      <c r="J14" s="18"/>
-      <c r="K14" s="16">
+      <c r="J14" s="23"/>
+      <c r="K14" s="9">
         <v>100</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="9">
         <v>24816</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="9">
         <v>4.03</v>
       </c>
-      <c r="N14" s="16">
+      <c r="N14" s="9">
         <v>45.12</v>
       </c>
-      <c r="O14" s="16">
+      <c r="O14" s="9">
         <v>371821</v>
       </c>
-      <c r="P14" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="10"/>
+      <c r="P14" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="20"/>
       <c r="R14" s="4">
         <v>100</v>
       </c>
@@ -3683,7 +3702,7 @@
       <c r="W14" s="6">
         <v>0</v>
       </c>
-      <c r="Y14" s="25"/>
+      <c r="Y14" s="15"/>
       <c r="Z14" s="4">
         <v>100</v>
       </c>
@@ -3707,7 +3726,7 @@
       <c r="B15" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="20"/>
       <c r="D15" s="4">
         <v>200</v>
       </c>
@@ -3726,26 +3745,26 @@
       <c r="I15" s="6">
         <v>0</v>
       </c>
-      <c r="J15" s="18"/>
-      <c r="K15" s="16">
+      <c r="J15" s="23"/>
+      <c r="K15" s="9">
         <v>200</v>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="9">
         <v>24086</v>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="9">
         <v>8.31</v>
       </c>
-      <c r="N15" s="16">
+      <c r="N15" s="9">
         <v>82.26</v>
       </c>
-      <c r="O15" s="16">
+      <c r="O15" s="9">
         <v>360128</v>
       </c>
-      <c r="P15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="10"/>
+      <c r="P15" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="20"/>
       <c r="R15" s="4">
         <v>200</v>
       </c>
@@ -3764,7 +3783,7 @@
       <c r="W15" s="6">
         <v>0</v>
       </c>
-      <c r="Y15" s="25"/>
+      <c r="Y15" s="15"/>
       <c r="Z15" s="4">
         <v>200</v>
       </c>
@@ -3788,7 +3807,7 @@
       <c r="B16" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="10"/>
+      <c r="C16" s="20"/>
       <c r="D16" s="4">
         <v>500</v>
       </c>
@@ -3807,26 +3826,26 @@
       <c r="I16" s="6">
         <v>0</v>
       </c>
-      <c r="J16" s="18"/>
-      <c r="K16" s="16">
+      <c r="J16" s="23"/>
+      <c r="K16" s="9">
         <v>500</v>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="9">
         <v>21696</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="9">
         <v>23.05</v>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="9">
         <v>123.81</v>
       </c>
-      <c r="O16" s="16">
+      <c r="O16" s="9">
         <v>323606</v>
       </c>
-      <c r="P16" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="10"/>
+      <c r="P16" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="20"/>
       <c r="R16" s="4">
         <v>500</v>
       </c>
@@ -3845,7 +3864,7 @@
       <c r="W16" s="6">
         <v>0</v>
       </c>
-      <c r="Y16" s="25"/>
+      <c r="Y16" s="15"/>
       <c r="Z16" s="4">
         <v>500</v>
       </c>
@@ -3869,7 +3888,7 @@
       <c r="B17" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="10"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="4">
         <v>1000</v>
       </c>
@@ -3888,26 +3907,26 @@
       <c r="I17" s="6">
         <v>0</v>
       </c>
-      <c r="J17" s="18"/>
-      <c r="K17" s="16">
+      <c r="J17" s="23"/>
+      <c r="K17" s="9">
         <v>1000</v>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="9">
         <v>20946</v>
       </c>
-      <c r="M17" s="16">
+      <c r="M17" s="9">
         <v>47.74</v>
       </c>
-      <c r="N17" s="16">
+      <c r="N17" s="9">
         <v>228</v>
       </c>
-      <c r="O17" s="16">
+      <c r="O17" s="9">
         <v>313096</v>
       </c>
-      <c r="P17" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="10"/>
+      <c r="P17" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="20"/>
       <c r="R17" s="4">
         <v>1000</v>
       </c>
@@ -3926,7 +3945,7 @@
       <c r="W17" s="6">
         <v>0</v>
       </c>
-      <c r="Y17" s="25"/>
+      <c r="Y17" s="15"/>
       <c r="Z17" s="4">
         <v>1000</v>
       </c>
@@ -3950,7 +3969,7 @@
       <c r="B18" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="21" t="s">
         <v>68</v>
       </c>
       <c r="D18" s="4">
@@ -3971,28 +3990,28 @@
       <c r="I18" s="6">
         <v>0</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="9">
         <v>50</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="9">
         <v>25536</v>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="9">
         <v>1.96</v>
       </c>
-      <c r="N18" s="16">
+      <c r="N18" s="9">
         <v>40.44</v>
       </c>
-      <c r="O18" s="16">
+      <c r="O18" s="9">
         <v>383064</v>
       </c>
-      <c r="P18" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="9" t="s">
+      <c r="P18" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="21" t="s">
         <v>68</v>
       </c>
       <c r="R18" s="4">
@@ -4013,7 +4032,7 @@
       <c r="W18" s="6">
         <v>0</v>
       </c>
-      <c r="Y18" s="26" t="s">
+      <c r="Y18" s="14" t="s">
         <v>68</v>
       </c>
       <c r="Z18" s="4">
@@ -4039,7 +4058,7 @@
       <c r="B19" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="4">
         <v>100</v>
       </c>
@@ -4058,26 +4077,26 @@
       <c r="I19" s="6">
         <v>0</v>
       </c>
-      <c r="J19" s="18"/>
-      <c r="K19" s="16">
+      <c r="J19" s="23"/>
+      <c r="K19" s="9">
         <v>100</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="9">
         <v>25419</v>
       </c>
-      <c r="M19" s="16">
+      <c r="M19" s="9">
         <v>3.94</v>
       </c>
-      <c r="N19" s="16">
+      <c r="N19" s="9">
         <v>62.22</v>
       </c>
-      <c r="O19" s="16">
+      <c r="O19" s="9">
         <v>380378</v>
       </c>
-      <c r="P19" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="10"/>
+      <c r="P19" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="20"/>
       <c r="R19" s="4">
         <v>100</v>
       </c>
@@ -4096,7 +4115,7 @@
       <c r="W19" s="6">
         <v>0</v>
       </c>
-      <c r="Y19" s="25"/>
+      <c r="Y19" s="15"/>
       <c r="Z19" s="4">
         <v>100</v>
       </c>
@@ -4120,7 +4139,7 @@
       <c r="B20" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="10"/>
+      <c r="C20" s="20"/>
       <c r="D20" s="4">
         <v>200</v>
       </c>
@@ -4139,26 +4158,26 @@
       <c r="I20" s="6">
         <v>0</v>
       </c>
-      <c r="J20" s="18"/>
-      <c r="K20" s="16">
+      <c r="J20" s="23"/>
+      <c r="K20" s="9">
         <v>200</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="9">
         <v>23853</v>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="9">
         <v>8.39</v>
       </c>
-      <c r="N20" s="16">
+      <c r="N20" s="9">
         <v>85.45</v>
       </c>
-      <c r="O20" s="16">
+      <c r="O20" s="9">
         <v>356914</v>
       </c>
-      <c r="P20" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="10"/>
+      <c r="P20" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="20"/>
       <c r="R20" s="4">
         <v>200</v>
       </c>
@@ -4177,7 +4196,7 @@
       <c r="W20" s="6">
         <v>0</v>
       </c>
-      <c r="Y20" s="25"/>
+      <c r="Y20" s="15"/>
       <c r="Z20" s="4">
         <v>200</v>
       </c>
@@ -4201,7 +4220,7 @@
       <c r="B21" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="20"/>
       <c r="D21" s="4">
         <v>500</v>
       </c>
@@ -4220,26 +4239,26 @@
       <c r="I21" s="6">
         <v>0</v>
       </c>
-      <c r="J21" s="18"/>
-      <c r="K21" s="16">
+      <c r="J21" s="23"/>
+      <c r="K21" s="9">
         <v>500</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="9">
         <v>21867</v>
       </c>
-      <c r="M21" s="16">
+      <c r="M21" s="9">
         <v>22.87</v>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="9">
         <v>149.93</v>
       </c>
-      <c r="O21" s="16">
+      <c r="O21" s="9">
         <v>326694</v>
       </c>
-      <c r="P21" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="10"/>
+      <c r="P21" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="20"/>
       <c r="R21" s="4">
         <v>500</v>
       </c>
@@ -4258,7 +4277,7 @@
       <c r="W21" s="6">
         <v>0</v>
       </c>
-      <c r="Y21" s="25"/>
+      <c r="Y21" s="15"/>
       <c r="Z21" s="4">
         <v>500</v>
       </c>
@@ -4282,7 +4301,7 @@
       <c r="B22" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="10"/>
+      <c r="C22" s="20"/>
       <c r="D22" s="4">
         <v>1000</v>
       </c>
@@ -4301,26 +4320,26 @@
       <c r="I22" s="6">
         <v>0</v>
       </c>
-      <c r="J22" s="18"/>
-      <c r="K22" s="16">
+      <c r="J22" s="23"/>
+      <c r="K22" s="9">
         <v>1000</v>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="9">
         <v>20993</v>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="9">
         <v>47.62</v>
       </c>
-      <c r="N22" s="16">
+      <c r="N22" s="9">
         <v>232.12</v>
       </c>
-      <c r="O22" s="16">
+      <c r="O22" s="9">
         <v>314041</v>
       </c>
-      <c r="P22" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="10"/>
+      <c r="P22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="20"/>
       <c r="R22" s="4">
         <v>1000</v>
       </c>
@@ -4339,7 +4358,7 @@
       <c r="W22" s="6">
         <v>0</v>
       </c>
-      <c r="Y22" s="25"/>
+      <c r="Y22" s="15"/>
       <c r="Z22" s="4">
         <v>1000</v>
       </c>
@@ -4363,7 +4382,7 @@
       <c r="B23" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D23" s="4">
@@ -4384,49 +4403,49 @@
       <c r="I23" s="6">
         <v>0</v>
       </c>
-      <c r="J23" s="15" t="s">
+      <c r="J23" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="9">
         <v>50</v>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="9">
         <v>25712</v>
       </c>
-      <c r="M23" s="16">
+      <c r="M23" s="9">
         <v>1.94</v>
       </c>
-      <c r="N23" s="16">
+      <c r="N23" s="9">
         <v>27.34</v>
       </c>
-      <c r="O23" s="16">
+      <c r="O23" s="9">
         <v>385692</v>
       </c>
-      <c r="P23" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="9" t="s">
+      <c r="P23" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="R23" s="4">
+      <c r="R23" s="28">
         <v>50</v>
       </c>
-      <c r="S23" s="4">
+      <c r="S23" s="28">
         <v>12424</v>
       </c>
-      <c r="T23" s="4">
+      <c r="T23" s="28">
         <v>4.0199999999999996</v>
       </c>
-      <c r="U23" s="4">
+      <c r="U23" s="28">
         <v>32.39</v>
       </c>
-      <c r="V23" s="4">
+      <c r="V23" s="28">
         <v>186393</v>
       </c>
-      <c r="W23" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="26" t="s">
+      <c r="W23" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="14" t="s">
         <v>47</v>
       </c>
       <c r="Z23" s="4">
@@ -4452,7 +4471,7 @@
       <c r="B24" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="10"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="4">
         <v>100</v>
       </c>
@@ -4471,45 +4490,45 @@
       <c r="I24" s="6">
         <v>0</v>
       </c>
-      <c r="J24" s="18"/>
-      <c r="K24" s="16">
+      <c r="J24" s="23"/>
+      <c r="K24" s="9">
         <v>100</v>
       </c>
-      <c r="L24" s="16">
+      <c r="L24" s="9">
         <v>25570</v>
       </c>
-      <c r="M24" s="16">
+      <c r="M24" s="9">
         <v>3.91</v>
       </c>
-      <c r="N24" s="16">
+      <c r="N24" s="9">
         <v>30.49</v>
       </c>
-      <c r="O24" s="16">
+      <c r="O24" s="9">
         <v>383572</v>
       </c>
-      <c r="P24" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="4">
+      <c r="P24" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="28">
         <v>100</v>
       </c>
-      <c r="S24" s="4">
+      <c r="S24" s="28">
         <v>13359</v>
       </c>
-      <c r="T24" s="4">
+      <c r="T24" s="28">
         <v>7.49</v>
       </c>
-      <c r="U24" s="4">
+      <c r="U24" s="28">
         <v>55.73</v>
       </c>
-      <c r="V24" s="4">
+      <c r="V24" s="28">
         <v>200049</v>
       </c>
-      <c r="W24" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="25"/>
+      <c r="W24" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="15"/>
       <c r="Z24" s="4">
         <v>100</v>
       </c>
@@ -4533,7 +4552,7 @@
       <c r="B25" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="20"/>
       <c r="D25" s="4">
         <v>200</v>
       </c>
@@ -4552,45 +4571,45 @@
       <c r="I25" s="6">
         <v>0</v>
       </c>
-      <c r="J25" s="18"/>
-      <c r="K25" s="16">
+      <c r="J25" s="23"/>
+      <c r="K25" s="9">
         <v>200</v>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="9">
         <v>24236</v>
       </c>
-      <c r="M25" s="16">
+      <c r="M25" s="9">
         <v>8.26</v>
       </c>
-      <c r="N25" s="16">
+      <c r="N25" s="9">
         <v>86.09</v>
       </c>
-      <c r="O25" s="16">
+      <c r="O25" s="9">
         <v>362100</v>
       </c>
-      <c r="P25" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="4">
+      <c r="P25" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="30"/>
+      <c r="R25" s="28">
         <v>200</v>
       </c>
-      <c r="S25" s="4">
+      <c r="S25" s="28">
         <v>13693</v>
       </c>
-      <c r="T25" s="4">
+      <c r="T25" s="28">
         <v>14.63</v>
       </c>
-      <c r="U25" s="4">
+      <c r="U25" s="28">
         <v>75.06</v>
       </c>
-      <c r="V25" s="4">
+      <c r="V25" s="28">
         <v>204495</v>
       </c>
-      <c r="W25" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="25"/>
+      <c r="W25" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="15"/>
       <c r="Z25" s="4">
         <v>200</v>
       </c>
@@ -4614,7 +4633,7 @@
       <c r="B26" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="10"/>
+      <c r="C26" s="20"/>
       <c r="D26" s="4">
         <v>500</v>
       </c>
@@ -4633,45 +4652,45 @@
       <c r="I26" s="6">
         <v>0</v>
       </c>
-      <c r="J26" s="18"/>
-      <c r="K26" s="16">
+      <c r="J26" s="23"/>
+      <c r="K26" s="9">
         <v>500</v>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="9">
         <v>22500</v>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="9">
         <v>22.23</v>
       </c>
-      <c r="N26" s="16">
+      <c r="N26" s="9">
         <v>140.35</v>
       </c>
-      <c r="O26" s="16">
+      <c r="O26" s="9">
         <v>336047</v>
       </c>
-      <c r="P26" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="4">
+      <c r="P26" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="28">
         <v>500</v>
       </c>
-      <c r="S26" s="4">
+      <c r="S26" s="28">
         <v>14177</v>
       </c>
-      <c r="T26" s="4">
+      <c r="T26" s="28">
         <v>35.270000000000003</v>
       </c>
-      <c r="U26" s="4">
+      <c r="U26" s="28">
         <v>139.57</v>
       </c>
-      <c r="V26" s="4">
+      <c r="V26" s="28">
         <v>212110</v>
       </c>
-      <c r="W26" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="25"/>
+      <c r="W26" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="15"/>
       <c r="Z26" s="4">
         <v>500</v>
       </c>
@@ -4695,7 +4714,7 @@
       <c r="B27" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="20"/>
       <c r="D27" s="4">
         <v>1000</v>
       </c>
@@ -4714,45 +4733,45 @@
       <c r="I27" s="6">
         <v>0</v>
       </c>
-      <c r="J27" s="18"/>
-      <c r="K27" s="16">
+      <c r="J27" s="23"/>
+      <c r="K27" s="9">
         <v>1000</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="9">
         <v>21066</v>
       </c>
-      <c r="M27" s="16">
+      <c r="M27" s="9">
         <v>47.51</v>
       </c>
-      <c r="N27" s="16">
+      <c r="N27" s="9">
         <v>203.4</v>
       </c>
-      <c r="O27" s="16">
+      <c r="O27" s="9">
         <v>314214</v>
       </c>
-      <c r="P27" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="4">
+      <c r="P27" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="30"/>
+      <c r="R27" s="28">
         <v>1000</v>
       </c>
-      <c r="S27" s="4">
+      <c r="S27" s="28">
         <v>13968</v>
       </c>
-      <c r="T27" s="4">
+      <c r="T27" s="28">
         <v>71.45</v>
       </c>
-      <c r="U27" s="4">
+      <c r="U27" s="28">
         <v>190.21</v>
       </c>
-      <c r="V27" s="4">
+      <c r="V27" s="28">
         <v>209464</v>
       </c>
-      <c r="W27" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="25"/>
+      <c r="W27" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="15"/>
       <c r="Z27" s="4">
         <v>1000</v>
       </c>
@@ -4776,7 +4795,7 @@
       <c r="B28" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="21" t="s">
         <v>48</v>
       </c>
       <c r="D28" s="4">
@@ -4797,49 +4816,49 @@
       <c r="I28" s="6">
         <v>0</v>
       </c>
-      <c r="J28" s="19" t="s">
+      <c r="J28" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="K28" s="20">
+      <c r="K28" s="11">
         <v>50</v>
       </c>
-      <c r="L28" s="20">
+      <c r="L28" s="11">
         <v>26283</v>
       </c>
-      <c r="M28" s="20">
+      <c r="M28" s="11">
         <v>1.9</v>
       </c>
-      <c r="N28" s="20">
+      <c r="N28" s="11">
         <v>25.37</v>
       </c>
-      <c r="O28" s="20">
+      <c r="O28" s="11">
         <v>394274</v>
       </c>
-      <c r="P28" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="9" t="s">
+      <c r="P28" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="R28" s="4">
+      <c r="R28" s="28">
         <v>50</v>
       </c>
-      <c r="S28" s="4">
+      <c r="S28" s="28">
         <v>4555</v>
       </c>
-      <c r="T28" s="4">
+      <c r="T28" s="28">
         <v>10.97</v>
       </c>
-      <c r="U28" s="4">
+      <c r="U28" s="28">
         <v>51.35</v>
       </c>
-      <c r="V28" s="4">
+      <c r="V28" s="28">
         <v>68380</v>
       </c>
-      <c r="W28" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="26" t="s">
+      <c r="W28" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="14" t="s">
         <v>48</v>
       </c>
       <c r="Z28" s="4">
@@ -4865,7 +4884,7 @@
       <c r="B29" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="20"/>
       <c r="D29" s="4">
         <v>100</v>
       </c>
@@ -4884,45 +4903,45 @@
       <c r="I29" s="6">
         <v>0</v>
       </c>
-      <c r="J29" s="22"/>
-      <c r="K29" s="20">
+      <c r="J29" s="25"/>
+      <c r="K29" s="11">
         <v>100</v>
       </c>
-      <c r="L29" s="20">
+      <c r="L29" s="11">
         <v>25212</v>
       </c>
-      <c r="M29" s="20">
+      <c r="M29" s="11">
         <v>3.97</v>
       </c>
-      <c r="N29" s="20">
+      <c r="N29" s="11">
         <v>41.7</v>
       </c>
-      <c r="O29" s="20">
+      <c r="O29" s="11">
         <v>377793</v>
       </c>
-      <c r="P29" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="4">
+      <c r="P29" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="28">
         <v>100</v>
       </c>
-      <c r="S29" s="4">
+      <c r="S29" s="28">
         <v>4575</v>
       </c>
-      <c r="T29" s="4">
+      <c r="T29" s="28">
         <v>21.84</v>
       </c>
-      <c r="U29" s="4">
+      <c r="U29" s="28">
         <v>77.069999999999993</v>
       </c>
-      <c r="V29" s="4">
+      <c r="V29" s="28">
         <v>68633</v>
       </c>
-      <c r="W29" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="25"/>
+      <c r="W29" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="15"/>
       <c r="Z29" s="4">
         <v>100</v>
       </c>
@@ -4946,7 +4965,7 @@
       <c r="B30" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="10"/>
+      <c r="C30" s="20"/>
       <c r="D30" s="4">
         <v>200</v>
       </c>
@@ -4965,45 +4984,45 @@
       <c r="I30" s="6">
         <v>0</v>
       </c>
-      <c r="J30" s="22"/>
-      <c r="K30" s="20">
+      <c r="J30" s="25"/>
+      <c r="K30" s="11">
         <v>200</v>
       </c>
-      <c r="L30" s="20">
+      <c r="L30" s="11">
         <v>24051</v>
       </c>
-      <c r="M30" s="20">
+      <c r="M30" s="11">
         <v>8.32</v>
       </c>
-      <c r="N30" s="20">
+      <c r="N30" s="11">
         <v>98.93</v>
       </c>
-      <c r="O30" s="20">
+      <c r="O30" s="11">
         <v>359804</v>
       </c>
-      <c r="P30" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="4">
+      <c r="P30" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="28">
         <v>200</v>
       </c>
-      <c r="S30" s="4">
+      <c r="S30" s="28">
         <v>4545</v>
       </c>
-      <c r="T30" s="4">
+      <c r="T30" s="28">
         <v>43.9</v>
       </c>
-      <c r="U30" s="4">
+      <c r="U30" s="28">
         <v>145.65</v>
       </c>
-      <c r="V30" s="4">
+      <c r="V30" s="28">
         <v>68256</v>
       </c>
-      <c r="W30" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="25"/>
+      <c r="W30" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="15"/>
       <c r="Z30" s="4">
         <v>200</v>
       </c>
@@ -5027,7 +5046,7 @@
       <c r="B31" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="20"/>
       <c r="D31" s="4">
         <v>500</v>
       </c>
@@ -5046,45 +5065,45 @@
       <c r="I31" s="6">
         <v>0</v>
       </c>
-      <c r="J31" s="22"/>
-      <c r="K31" s="20">
+      <c r="J31" s="25"/>
+      <c r="K31" s="11">
         <v>500</v>
       </c>
-      <c r="L31" s="20">
+      <c r="L31" s="11">
         <v>22248</v>
       </c>
-      <c r="M31" s="20">
+      <c r="M31" s="11">
         <v>22.5</v>
       </c>
-      <c r="N31" s="20">
+      <c r="N31" s="11">
         <v>157.88</v>
       </c>
-      <c r="O31" s="20">
+      <c r="O31" s="11">
         <v>331593</v>
       </c>
-      <c r="P31" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="4">
+      <c r="P31" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="28">
         <v>500</v>
       </c>
-      <c r="S31" s="4">
+      <c r="S31" s="28">
         <v>4550</v>
       </c>
-      <c r="T31" s="4">
+      <c r="T31" s="28">
         <v>109.28</v>
       </c>
-      <c r="U31" s="4">
+      <c r="U31" s="28">
         <v>227.83</v>
       </c>
-      <c r="V31" s="4">
+      <c r="V31" s="28">
         <v>68558</v>
       </c>
-      <c r="W31" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="25"/>
+      <c r="W31" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="15"/>
       <c r="Z31" s="4">
         <v>500</v>
       </c>
@@ -5108,7 +5127,7 @@
       <c r="B32" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="10"/>
+      <c r="C32" s="20"/>
       <c r="D32" s="4">
         <v>1000</v>
       </c>
@@ -5127,45 +5146,45 @@
       <c r="I32" s="6">
         <v>0</v>
       </c>
-      <c r="J32" s="22"/>
-      <c r="K32" s="20">
+      <c r="J32" s="25"/>
+      <c r="K32" s="11">
         <v>1000</v>
       </c>
-      <c r="L32" s="20">
+      <c r="L32" s="11">
         <v>21302</v>
       </c>
-      <c r="M32" s="20">
+      <c r="M32" s="11">
         <v>46.92</v>
       </c>
-      <c r="N32" s="20">
+      <c r="N32" s="11">
         <v>205.16</v>
       </c>
-      <c r="O32" s="20">
+      <c r="O32" s="11">
         <v>318099</v>
       </c>
-      <c r="P32" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="4">
+      <c r="P32" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="28">
         <v>1000</v>
       </c>
-      <c r="S32" s="4">
+      <c r="S32" s="28">
         <v>4560</v>
       </c>
-      <c r="T32" s="4">
+      <c r="T32" s="28">
         <v>217.96</v>
       </c>
-      <c r="U32" s="4">
+      <c r="U32" s="28">
         <v>555.86</v>
       </c>
-      <c r="V32" s="4">
+      <c r="V32" s="28">
         <v>68927</v>
       </c>
-      <c r="W32" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="25"/>
+      <c r="W32" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="15"/>
       <c r="Z32" s="4">
         <v>1000</v>
       </c>
@@ -5189,7 +5208,7 @@
       <c r="B33" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="21" t="s">
         <v>49</v>
       </c>
       <c r="D33" s="4">
@@ -5210,49 +5229,49 @@
       <c r="I33" s="6">
         <v>0</v>
       </c>
-      <c r="J33" s="19" t="s">
+      <c r="J33" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="K33" s="20">
+      <c r="K33" s="11">
         <v>50</v>
       </c>
-      <c r="L33" s="20">
+      <c r="L33" s="11">
         <v>26265</v>
       </c>
-      <c r="M33" s="20">
+      <c r="M33" s="11">
         <v>1.9</v>
       </c>
-      <c r="N33" s="20">
+      <c r="N33" s="11">
         <v>36.9</v>
       </c>
-      <c r="O33" s="20">
+      <c r="O33" s="11">
         <v>393985</v>
       </c>
-      <c r="P33" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="9" t="s">
+      <c r="P33" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="R33" s="4">
+      <c r="R33" s="28">
         <v>50</v>
       </c>
-      <c r="S33" s="4">
+      <c r="S33" s="28">
         <v>4626</v>
       </c>
-      <c r="T33" s="4">
+      <c r="T33" s="28">
         <v>10.8</v>
       </c>
-      <c r="U33" s="4">
+      <c r="U33" s="28">
         <v>44.74</v>
       </c>
-      <c r="V33" s="4">
+      <c r="V33" s="28">
         <v>69439</v>
       </c>
-      <c r="W33" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="26" t="s">
+      <c r="W33" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="14" t="s">
         <v>49</v>
       </c>
       <c r="Z33" s="4">
@@ -5278,7 +5297,7 @@
       <c r="B34" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="10"/>
+      <c r="C34" s="20"/>
       <c r="D34" s="4">
         <v>100</v>
       </c>
@@ -5297,45 +5316,45 @@
       <c r="I34" s="6">
         <v>0</v>
       </c>
-      <c r="J34" s="22"/>
-      <c r="K34" s="20">
+      <c r="J34" s="25"/>
+      <c r="K34" s="11">
         <v>100</v>
       </c>
-      <c r="L34" s="20">
+      <c r="L34" s="11">
         <v>25644</v>
       </c>
-      <c r="M34" s="20">
+      <c r="M34" s="11">
         <v>3.9</v>
       </c>
-      <c r="N34" s="20">
+      <c r="N34" s="11">
         <v>50.2</v>
       </c>
-      <c r="O34" s="20">
+      <c r="O34" s="11">
         <v>384223</v>
       </c>
-      <c r="P34" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="4">
+      <c r="P34" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="28">
         <v>100</v>
       </c>
-      <c r="S34" s="4">
+      <c r="S34" s="28">
         <v>4521</v>
       </c>
-      <c r="T34" s="4">
+      <c r="T34" s="28">
         <v>22.1</v>
       </c>
-      <c r="U34" s="4">
+      <c r="U34" s="28">
         <v>94.92</v>
       </c>
-      <c r="V34" s="4">
+      <c r="V34" s="28">
         <v>67837</v>
       </c>
-      <c r="W34" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="25"/>
+      <c r="W34" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="15"/>
       <c r="Z34" s="4">
         <v>100</v>
       </c>
@@ -5359,7 +5378,7 @@
       <c r="B35" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="20"/>
       <c r="D35" s="4">
         <v>200</v>
       </c>
@@ -5378,45 +5397,45 @@
       <c r="I35" s="6">
         <v>0</v>
       </c>
-      <c r="J35" s="22"/>
-      <c r="K35" s="20">
+      <c r="J35" s="25"/>
+      <c r="K35" s="11">
         <v>200</v>
       </c>
-      <c r="L35" s="20">
+      <c r="L35" s="11">
         <v>24487</v>
       </c>
-      <c r="M35" s="20">
+      <c r="M35" s="11">
         <v>8.16</v>
       </c>
-      <c r="N35" s="20">
+      <c r="N35" s="11">
         <v>66.38</v>
       </c>
-      <c r="O35" s="20">
+      <c r="O35" s="11">
         <v>367049</v>
       </c>
-      <c r="P35" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="4">
+      <c r="P35" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="28">
         <v>200</v>
       </c>
-      <c r="S35" s="4">
+      <c r="S35" s="28">
         <v>4579</v>
       </c>
-      <c r="T35" s="4">
+      <c r="T35" s="28">
         <v>43.57</v>
       </c>
-      <c r="U35" s="4">
+      <c r="U35" s="28">
         <v>122.05</v>
       </c>
-      <c r="V35" s="4">
+      <c r="V35" s="28">
         <v>68819</v>
       </c>
-      <c r="W35" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="25"/>
+      <c r="W35" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="15"/>
       <c r="Z35" s="4">
         <v>200</v>
       </c>
@@ -5440,7 +5459,7 @@
       <c r="B36" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="10"/>
+      <c r="C36" s="20"/>
       <c r="D36" s="4">
         <v>500</v>
       </c>
@@ -5459,45 +5478,45 @@
       <c r="I36" s="6">
         <v>0</v>
       </c>
-      <c r="J36" s="22"/>
-      <c r="K36" s="20">
+      <c r="J36" s="25"/>
+      <c r="K36" s="11">
         <v>500</v>
       </c>
-      <c r="L36" s="20">
+      <c r="L36" s="11">
         <v>22460</v>
       </c>
-      <c r="M36" s="20">
+      <c r="M36" s="11">
         <v>22.24</v>
       </c>
-      <c r="N36" s="20">
+      <c r="N36" s="11">
         <v>165.02</v>
       </c>
-      <c r="O36" s="20">
+      <c r="O36" s="11">
         <v>335985</v>
       </c>
-      <c r="P36" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="4">
+      <c r="P36" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="28">
         <v>500</v>
       </c>
-      <c r="S36" s="4">
+      <c r="S36" s="28">
         <v>4542</v>
       </c>
-      <c r="T36" s="4">
+      <c r="T36" s="28">
         <v>109.57</v>
       </c>
-      <c r="U36" s="4">
+      <c r="U36" s="28">
         <v>287.35000000000002</v>
       </c>
-      <c r="V36" s="4">
+      <c r="V36" s="28">
         <v>68441</v>
       </c>
-      <c r="W36" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="25"/>
+      <c r="W36" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="15"/>
       <c r="Z36" s="4">
         <v>500</v>
       </c>
@@ -5521,7 +5540,7 @@
       <c r="B37" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="10"/>
+      <c r="C37" s="20"/>
       <c r="D37" s="4">
         <v>1000</v>
       </c>
@@ -5540,45 +5559,45 @@
       <c r="I37" s="6">
         <v>0</v>
       </c>
-      <c r="J37" s="22"/>
-      <c r="K37" s="20">
+      <c r="J37" s="25"/>
+      <c r="K37" s="11">
         <v>1000</v>
       </c>
-      <c r="L37" s="20">
+      <c r="L37" s="11">
         <v>21437</v>
       </c>
-      <c r="M37" s="20">
+      <c r="M37" s="11">
         <v>46.65</v>
       </c>
-      <c r="N37" s="20">
+      <c r="N37" s="11">
         <v>215.1</v>
       </c>
-      <c r="O37" s="20">
+      <c r="O37" s="11">
         <v>320023</v>
       </c>
-      <c r="P37" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="10"/>
-      <c r="R37" s="4">
+      <c r="P37" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="28">
         <v>1000</v>
       </c>
-      <c r="S37" s="4">
+      <c r="S37" s="28">
         <v>4516</v>
       </c>
-      <c r="T37" s="4">
+      <c r="T37" s="28">
         <v>219.82</v>
       </c>
-      <c r="U37" s="4">
+      <c r="U37" s="28">
         <v>459.31</v>
       </c>
-      <c r="V37" s="4">
+      <c r="V37" s="28">
         <v>68243</v>
       </c>
-      <c r="W37" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="25"/>
+      <c r="W37" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="15"/>
       <c r="Z37" s="4">
         <v>1000</v>
       </c>
@@ -5602,7 +5621,7 @@
       <c r="B38" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="20" t="s">
         <v>50</v>
       </c>
       <c r="D38" s="4">
@@ -5623,7 +5642,7 @@
       <c r="I38" s="6">
         <v>0</v>
       </c>
-      <c r="J38" s="10" t="s">
+      <c r="J38" s="20" t="s">
         <v>94</v>
       </c>
       <c r="K38" s="4">
@@ -5644,7 +5663,7 @@
       <c r="P38" s="6">
         <v>0</v>
       </c>
-      <c r="Q38" s="10" t="s">
+      <c r="Q38" s="20" t="s">
         <v>50</v>
       </c>
       <c r="R38" s="4">
@@ -5665,7 +5684,7 @@
       <c r="W38" s="6">
         <v>0</v>
       </c>
-      <c r="Y38" s="25" t="s">
+      <c r="Y38" s="15" t="s">
         <v>50</v>
       </c>
       <c r="Z38" s="4">
@@ -5691,7 +5710,7 @@
       <c r="B39" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="20"/>
       <c r="D39" s="4">
         <v>100</v>
       </c>
@@ -5710,7 +5729,7 @@
       <c r="I39" s="6">
         <v>0</v>
       </c>
-      <c r="J39" s="10"/>
+      <c r="J39" s="20"/>
       <c r="K39" s="4">
         <v>100</v>
       </c>
@@ -5729,7 +5748,7 @@
       <c r="P39" s="6">
         <v>0</v>
       </c>
-      <c r="Q39" s="10"/>
+      <c r="Q39" s="20"/>
       <c r="R39" s="4">
         <v>100</v>
       </c>
@@ -5748,7 +5767,7 @@
       <c r="W39" s="6">
         <v>0</v>
       </c>
-      <c r="Y39" s="25"/>
+      <c r="Y39" s="15"/>
       <c r="Z39" s="4">
         <v>100</v>
       </c>
@@ -5772,7 +5791,7 @@
       <c r="B40" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="10"/>
+      <c r="C40" s="20"/>
       <c r="D40" s="4">
         <v>200</v>
       </c>
@@ -5791,7 +5810,7 @@
       <c r="I40" s="6">
         <v>0</v>
       </c>
-      <c r="J40" s="10"/>
+      <c r="J40" s="20"/>
       <c r="K40" s="4">
         <v>200</v>
       </c>
@@ -5810,7 +5829,7 @@
       <c r="P40" s="6">
         <v>0</v>
       </c>
-      <c r="Q40" s="10"/>
+      <c r="Q40" s="20"/>
       <c r="R40" s="4">
         <v>200</v>
       </c>
@@ -5829,7 +5848,7 @@
       <c r="W40" s="6">
         <v>0</v>
       </c>
-      <c r="Y40" s="25"/>
+      <c r="Y40" s="15"/>
       <c r="Z40" s="4">
         <v>200</v>
       </c>
@@ -5853,7 +5872,7 @@
       <c r="B41" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="20"/>
       <c r="D41" s="4">
         <v>500</v>
       </c>
@@ -5872,7 +5891,7 @@
       <c r="I41" s="6">
         <v>0</v>
       </c>
-      <c r="J41" s="10"/>
+      <c r="J41" s="20"/>
       <c r="K41" s="4">
         <v>500</v>
       </c>
@@ -5891,7 +5910,7 @@
       <c r="P41" s="6">
         <v>0</v>
       </c>
-      <c r="Q41" s="10"/>
+      <c r="Q41" s="20"/>
       <c r="R41" s="4">
         <v>500</v>
       </c>
@@ -5910,7 +5929,7 @@
       <c r="W41" s="6">
         <v>0</v>
       </c>
-      <c r="Y41" s="25"/>
+      <c r="Y41" s="15"/>
       <c r="Z41" s="4">
         <v>500</v>
       </c>
@@ -5934,7 +5953,7 @@
       <c r="B42" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="10"/>
+      <c r="C42" s="20"/>
       <c r="D42" s="4">
         <v>1000</v>
       </c>
@@ -5953,7 +5972,7 @@
       <c r="I42" s="6">
         <v>0</v>
       </c>
-      <c r="J42" s="10"/>
+      <c r="J42" s="20"/>
       <c r="K42" s="4">
         <v>1000</v>
       </c>
@@ -5972,7 +5991,7 @@
       <c r="P42" s="6">
         <v>0</v>
       </c>
-      <c r="Q42" s="10"/>
+      <c r="Q42" s="20"/>
       <c r="R42" s="4">
         <v>1000</v>
       </c>
@@ -5991,7 +6010,7 @@
       <c r="W42" s="6">
         <v>0</v>
       </c>
-      <c r="Y42" s="25"/>
+      <c r="Y42" s="15"/>
       <c r="Z42" s="4">
         <v>1000</v>
       </c>
@@ -6015,7 +6034,7 @@
       <c r="B43" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="21" t="s">
         <v>51</v>
       </c>
       <c r="D43" s="4">
@@ -6036,28 +6055,28 @@
       <c r="I43" s="6">
         <v>0</v>
       </c>
-      <c r="J43" s="19" t="s">
+      <c r="J43" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="K43" s="20">
+      <c r="K43" s="11">
         <v>50</v>
       </c>
-      <c r="L43" s="20">
+      <c r="L43" s="11">
         <v>25733</v>
       </c>
-      <c r="M43" s="20">
+      <c r="M43" s="11">
         <v>1.94</v>
       </c>
-      <c r="N43" s="20">
+      <c r="N43" s="11">
         <v>30.14</v>
       </c>
-      <c r="O43" s="20">
+      <c r="O43" s="11">
         <v>386020</v>
       </c>
-      <c r="P43" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="9" t="s">
+      <c r="P43" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="21" t="s">
         <v>51</v>
       </c>
       <c r="R43" s="4">
@@ -6078,7 +6097,7 @@
       <c r="W43" s="6">
         <v>0</v>
       </c>
-      <c r="Y43" s="26" t="s">
+      <c r="Y43" s="14" t="s">
         <v>51</v>
       </c>
       <c r="Z43" s="4">
@@ -6104,7 +6123,7 @@
       <c r="B44" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="10"/>
+      <c r="C44" s="20"/>
       <c r="D44" s="4">
         <v>100</v>
       </c>
@@ -6123,26 +6142,26 @@
       <c r="I44" s="6">
         <v>0</v>
       </c>
-      <c r="J44" s="22"/>
-      <c r="K44" s="20">
+      <c r="J44" s="25"/>
+      <c r="K44" s="11">
         <v>100</v>
       </c>
-      <c r="L44" s="20">
+      <c r="L44" s="11">
         <v>24674</v>
       </c>
-      <c r="M44" s="20">
+      <c r="M44" s="11">
         <v>4.05</v>
       </c>
-      <c r="N44" s="20">
+      <c r="N44" s="11">
         <v>42.14</v>
       </c>
-      <c r="O44" s="20">
+      <c r="O44" s="11">
         <v>369860</v>
       </c>
-      <c r="P44" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="10"/>
+      <c r="P44" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="20"/>
       <c r="R44" s="4">
         <v>100</v>
       </c>
@@ -6161,7 +6180,7 @@
       <c r="W44" s="6">
         <v>0</v>
       </c>
-      <c r="Y44" s="25"/>
+      <c r="Y44" s="15"/>
       <c r="Z44" s="4">
         <v>100</v>
       </c>
@@ -6185,7 +6204,7 @@
       <c r="B45" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="20"/>
       <c r="D45" s="4">
         <v>200</v>
       </c>
@@ -6204,26 +6223,26 @@
       <c r="I45" s="6">
         <v>0</v>
       </c>
-      <c r="J45" s="22"/>
-      <c r="K45" s="20">
+      <c r="J45" s="25"/>
+      <c r="K45" s="11">
         <v>200</v>
       </c>
-      <c r="L45" s="20">
+      <c r="L45" s="11">
         <v>24006</v>
       </c>
-      <c r="M45" s="20">
+      <c r="M45" s="11">
         <v>8.33</v>
       </c>
-      <c r="N45" s="20">
+      <c r="N45" s="11">
         <v>71.08</v>
       </c>
-      <c r="O45" s="20">
+      <c r="O45" s="11">
         <v>359049</v>
       </c>
-      <c r="P45" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="10"/>
+      <c r="P45" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="20"/>
       <c r="R45" s="4">
         <v>200</v>
       </c>
@@ -6242,7 +6261,7 @@
       <c r="W45" s="6">
         <v>0</v>
       </c>
-      <c r="Y45" s="25"/>
+      <c r="Y45" s="15"/>
       <c r="Z45" s="4">
         <v>200</v>
       </c>
@@ -6266,7 +6285,7 @@
       <c r="B46" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="10"/>
+      <c r="C46" s="20"/>
       <c r="D46" s="4">
         <v>500</v>
       </c>
@@ -6285,26 +6304,26 @@
       <c r="I46" s="6">
         <v>0</v>
       </c>
-      <c r="J46" s="22"/>
-      <c r="K46" s="20">
+      <c r="J46" s="25"/>
+      <c r="K46" s="11">
         <v>500</v>
       </c>
-      <c r="L46" s="20">
+      <c r="L46" s="11">
         <v>21934</v>
       </c>
-      <c r="M46" s="20">
+      <c r="M46" s="11">
         <v>22.8</v>
       </c>
-      <c r="N46" s="20">
+      <c r="N46" s="11">
         <v>148.15</v>
       </c>
-      <c r="O46" s="20">
+      <c r="O46" s="11">
         <v>327809</v>
       </c>
-      <c r="P46" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="10"/>
+      <c r="P46" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="20"/>
       <c r="R46" s="4">
         <v>500</v>
       </c>
@@ -6323,7 +6342,7 @@
       <c r="W46" s="6">
         <v>0</v>
       </c>
-      <c r="Y46" s="25"/>
+      <c r="Y46" s="15"/>
       <c r="Z46" s="4">
         <v>500</v>
       </c>
@@ -6347,7 +6366,7 @@
       <c r="B47" t="s">
         <v>15</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="20"/>
       <c r="D47" s="4">
         <v>1000</v>
       </c>
@@ -6366,26 +6385,26 @@
       <c r="I47" s="6">
         <v>0</v>
       </c>
-      <c r="J47" s="22"/>
-      <c r="K47" s="20">
+      <c r="J47" s="25"/>
+      <c r="K47" s="11">
         <v>1000</v>
       </c>
-      <c r="L47" s="20">
+      <c r="L47" s="11">
         <v>20873</v>
       </c>
-      <c r="M47" s="20">
+      <c r="M47" s="11">
         <v>47.93</v>
       </c>
-      <c r="N47" s="20">
+      <c r="N47" s="11">
         <v>217.69</v>
       </c>
-      <c r="O47" s="20">
+      <c r="O47" s="11">
         <v>311369</v>
       </c>
-      <c r="P47" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="10"/>
+      <c r="P47" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="20"/>
       <c r="R47" s="4">
         <v>1000</v>
       </c>
@@ -6404,7 +6423,7 @@
       <c r="W47" s="6">
         <v>0</v>
       </c>
-      <c r="Y47" s="25"/>
+      <c r="Y47" s="15"/>
       <c r="Z47" s="4">
         <v>1000</v>
       </c>
@@ -6428,7 +6447,7 @@
       <c r="B48" t="s">
         <v>16</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="20" t="s">
         <v>52</v>
       </c>
       <c r="D48" s="4">
@@ -6449,7 +6468,7 @@
       <c r="I48" s="6">
         <v>0</v>
       </c>
-      <c r="J48" s="9" t="s">
+      <c r="J48" s="21" t="s">
         <v>96</v>
       </c>
       <c r="K48" s="4">
@@ -6470,28 +6489,28 @@
       <c r="P48" s="6">
         <v>0</v>
       </c>
-      <c r="Q48" s="9" t="s">
+      <c r="Q48" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="R48" s="4">
+      <c r="R48" s="11">
         <v>50</v>
       </c>
-      <c r="S48" s="4">
+      <c r="S48" s="11">
         <v>3772</v>
       </c>
-      <c r="T48" s="4">
+      <c r="T48" s="11">
         <v>13.25</v>
       </c>
-      <c r="U48" s="4">
+      <c r="U48" s="11">
         <v>52.98</v>
       </c>
-      <c r="V48" s="4">
+      <c r="V48" s="11">
         <v>8958</v>
       </c>
-      <c r="W48" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="25" t="s">
+      <c r="W48" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="15" t="s">
         <v>52</v>
       </c>
       <c r="Z48" s="4">
@@ -6517,7 +6536,7 @@
       <c r="B49" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="20"/>
       <c r="D49" s="4">
         <v>100</v>
       </c>
@@ -6536,7 +6555,7 @@
       <c r="I49" s="6">
         <v>0</v>
       </c>
-      <c r="J49" s="10"/>
+      <c r="J49" s="20"/>
       <c r="K49" s="4">
         <v>100</v>
       </c>
@@ -6555,26 +6574,26 @@
       <c r="P49" s="6">
         <v>0</v>
       </c>
-      <c r="Q49" s="10"/>
-      <c r="R49" s="4">
+      <c r="Q49" s="25"/>
+      <c r="R49" s="11">
         <v>100</v>
       </c>
-      <c r="S49" s="4">
+      <c r="S49" s="11">
         <v>3361</v>
       </c>
-      <c r="T49" s="4">
+      <c r="T49" s="11">
         <v>29.78</v>
       </c>
-      <c r="U49" s="4">
+      <c r="U49" s="11">
         <v>94.6</v>
       </c>
-      <c r="V49" s="4">
+      <c r="V49" s="11">
         <v>50385</v>
       </c>
-      <c r="W49" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="25"/>
+      <c r="W49" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="15"/>
       <c r="Z49" s="4">
         <v>100</v>
       </c>
@@ -6598,7 +6617,7 @@
       <c r="B50" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="10"/>
+      <c r="C50" s="20"/>
       <c r="D50" s="4">
         <v>200</v>
       </c>
@@ -6617,7 +6636,7 @@
       <c r="I50" s="6">
         <v>0</v>
       </c>
-      <c r="J50" s="10"/>
+      <c r="J50" s="20"/>
       <c r="K50" s="4">
         <v>200</v>
       </c>
@@ -6636,26 +6655,26 @@
       <c r="P50" s="6">
         <v>0</v>
       </c>
-      <c r="Q50" s="10"/>
-      <c r="R50" s="4">
+      <c r="Q50" s="25"/>
+      <c r="R50" s="11">
         <v>200</v>
       </c>
-      <c r="S50" s="4">
+      <c r="S50" s="11">
         <v>3461</v>
       </c>
-      <c r="T50" s="4">
+      <c r="T50" s="11">
         <v>57.6</v>
       </c>
-      <c r="U50" s="4">
+      <c r="U50" s="11">
         <v>160.88999999999999</v>
       </c>
-      <c r="V50" s="4">
+      <c r="V50" s="11">
         <v>40735</v>
       </c>
-      <c r="W50" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="25"/>
+      <c r="W50" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="15"/>
       <c r="Z50" s="4">
         <v>200</v>
       </c>
@@ -6679,7 +6698,7 @@
       <c r="B51" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="10"/>
+      <c r="C51" s="20"/>
       <c r="D51" s="4">
         <v>500</v>
       </c>
@@ -6698,7 +6717,7 @@
       <c r="I51" s="6">
         <v>0</v>
       </c>
-      <c r="J51" s="10"/>
+      <c r="J51" s="20"/>
       <c r="K51" s="4">
         <v>500</v>
       </c>
@@ -6717,26 +6736,26 @@
       <c r="P51" s="6">
         <v>0</v>
       </c>
-      <c r="Q51" s="10"/>
-      <c r="R51" s="4">
+      <c r="Q51" s="25"/>
+      <c r="R51" s="11">
         <v>500</v>
       </c>
-      <c r="S51" s="4">
+      <c r="S51" s="11">
         <v>3881</v>
       </c>
-      <c r="T51" s="4">
+      <c r="T51" s="11">
         <v>128.22999999999999</v>
       </c>
-      <c r="U51" s="4">
+      <c r="U51" s="11">
         <v>257.81</v>
       </c>
-      <c r="V51" s="4">
-        <v>0</v>
-      </c>
-      <c r="W51" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="25"/>
+      <c r="V51" s="11">
+        <v>0</v>
+      </c>
+      <c r="W51" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="15"/>
       <c r="Z51" s="4">
         <v>500</v>
       </c>
@@ -6760,7 +6779,7 @@
       <c r="B52" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="10"/>
+      <c r="C52" s="20"/>
       <c r="D52" s="4">
         <v>1000</v>
       </c>
@@ -6779,7 +6798,7 @@
       <c r="I52" s="6">
         <v>0</v>
       </c>
-      <c r="J52" s="10"/>
+      <c r="J52" s="20"/>
       <c r="K52" s="4">
         <v>1000</v>
       </c>
@@ -6798,26 +6817,26 @@
       <c r="P52" s="6">
         <v>0</v>
       </c>
-      <c r="Q52" s="10"/>
-      <c r="R52" s="4">
+      <c r="Q52" s="25"/>
+      <c r="R52" s="11">
         <v>1000</v>
       </c>
-      <c r="S52" s="4">
+      <c r="S52" s="11">
         <v>3728</v>
       </c>
-      <c r="T52" s="4">
+      <c r="T52" s="11">
         <v>266.39</v>
       </c>
-      <c r="U52" s="4">
+      <c r="U52" s="11">
         <v>507.79</v>
       </c>
-      <c r="V52" s="4">
+      <c r="V52" s="11">
         <v>12679</v>
       </c>
-      <c r="W52" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="25"/>
+      <c r="W52" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="15"/>
       <c r="Z52" s="4">
         <v>1000</v>
       </c>
@@ -6841,7 +6860,7 @@
       <c r="B53" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D53" s="4">
@@ -6862,7 +6881,7 @@
       <c r="I53" s="6">
         <v>0</v>
       </c>
-      <c r="J53" s="9" t="s">
+      <c r="J53" s="21" t="s">
         <v>97</v>
       </c>
       <c r="K53" s="4">
@@ -6883,7 +6902,7 @@
       <c r="P53" s="6">
         <v>0</v>
       </c>
-      <c r="Q53" s="9" t="s">
+      <c r="Q53" s="21" t="s">
         <v>73</v>
       </c>
       <c r="R53" s="4">
@@ -6904,7 +6923,7 @@
       <c r="W53" s="6">
         <v>0</v>
       </c>
-      <c r="Y53" s="26" t="s">
+      <c r="Y53" s="14" t="s">
         <v>53</v>
       </c>
       <c r="Z53" s="4">
@@ -6930,7 +6949,7 @@
       <c r="B54" t="s">
         <v>17</v>
       </c>
-      <c r="C54" s="10"/>
+      <c r="C54" s="20"/>
       <c r="D54" s="4">
         <v>100</v>
       </c>
@@ -6949,7 +6968,7 @@
       <c r="I54" s="6">
         <v>0</v>
       </c>
-      <c r="J54" s="10"/>
+      <c r="J54" s="20"/>
       <c r="K54" s="4">
         <v>100</v>
       </c>
@@ -6968,7 +6987,7 @@
       <c r="P54" s="6">
         <v>0</v>
       </c>
-      <c r="Q54" s="10"/>
+      <c r="Q54" s="20"/>
       <c r="R54" s="4">
         <v>100</v>
       </c>
@@ -6987,7 +7006,7 @@
       <c r="W54" s="6">
         <v>0</v>
       </c>
-      <c r="Y54" s="25"/>
+      <c r="Y54" s="15"/>
       <c r="Z54" s="4">
         <v>100</v>
       </c>
@@ -7011,7 +7030,7 @@
       <c r="B55" t="s">
         <v>17</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="20"/>
       <c r="D55" s="4">
         <v>200</v>
       </c>
@@ -7030,7 +7049,7 @@
       <c r="I55" s="6">
         <v>0</v>
       </c>
-      <c r="J55" s="10"/>
+      <c r="J55" s="20"/>
       <c r="K55" s="4">
         <v>200</v>
       </c>
@@ -7049,7 +7068,7 @@
       <c r="P55" s="6">
         <v>0</v>
       </c>
-      <c r="Q55" s="10"/>
+      <c r="Q55" s="20"/>
       <c r="R55" s="4">
         <v>200</v>
       </c>
@@ -7068,7 +7087,7 @@
       <c r="W55" s="6">
         <v>0</v>
       </c>
-      <c r="Y55" s="25"/>
+      <c r="Y55" s="15"/>
       <c r="Z55" s="4">
         <v>200</v>
       </c>
@@ -7092,7 +7111,7 @@
       <c r="B56" t="s">
         <v>17</v>
       </c>
-      <c r="C56" s="10"/>
+      <c r="C56" s="20"/>
       <c r="D56" s="4">
         <v>500</v>
       </c>
@@ -7111,7 +7130,7 @@
       <c r="I56" s="6">
         <v>0</v>
       </c>
-      <c r="J56" s="10"/>
+      <c r="J56" s="20"/>
       <c r="K56" s="4">
         <v>500</v>
       </c>
@@ -7130,7 +7149,7 @@
       <c r="P56" s="6">
         <v>0</v>
       </c>
-      <c r="Q56" s="10"/>
+      <c r="Q56" s="20"/>
       <c r="R56" s="4">
         <v>500</v>
       </c>
@@ -7149,7 +7168,7 @@
       <c r="W56" s="6">
         <v>0</v>
       </c>
-      <c r="Y56" s="25"/>
+      <c r="Y56" s="15"/>
       <c r="Z56" s="4">
         <v>500</v>
       </c>
@@ -7173,7 +7192,7 @@
       <c r="B57" t="s">
         <v>17</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="20"/>
       <c r="D57" s="4">
         <v>1000</v>
       </c>
@@ -7192,7 +7211,7 @@
       <c r="I57" s="6">
         <v>0</v>
       </c>
-      <c r="J57" s="10"/>
+      <c r="J57" s="20"/>
       <c r="K57" s="4">
         <v>1000</v>
       </c>
@@ -7211,7 +7230,7 @@
       <c r="P57" s="6">
         <v>0</v>
       </c>
-      <c r="Q57" s="10"/>
+      <c r="Q57" s="20"/>
       <c r="R57" s="4">
         <v>1000</v>
       </c>
@@ -7230,7 +7249,7 @@
       <c r="W57" s="6">
         <v>0</v>
       </c>
-      <c r="Y57" s="25"/>
+      <c r="Y57" s="15"/>
       <c r="Z57" s="4">
         <v>1000</v>
       </c>
@@ -7254,7 +7273,7 @@
       <c r="B58" t="s">
         <v>18</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D58" s="4">
@@ -7275,7 +7294,7 @@
       <c r="I58" s="6">
         <v>0</v>
       </c>
-      <c r="J58" s="9" t="s">
+      <c r="J58" s="21" t="s">
         <v>97</v>
       </c>
       <c r="K58" s="4">
@@ -7296,7 +7315,7 @@
       <c r="P58" s="6">
         <v>0</v>
       </c>
-      <c r="Q58" s="9" t="s">
+      <c r="Q58" s="21" t="s">
         <v>73</v>
       </c>
       <c r="R58" s="4">
@@ -7317,7 +7336,7 @@
       <c r="W58" s="6">
         <v>0</v>
       </c>
-      <c r="Y58" s="26" t="s">
+      <c r="Y58" s="14" t="s">
         <v>53</v>
       </c>
       <c r="Z58" s="4">
@@ -7343,7 +7362,7 @@
       <c r="B59" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="20"/>
       <c r="D59" s="4">
         <v>100</v>
       </c>
@@ -7362,7 +7381,7 @@
       <c r="I59" s="6">
         <v>0</v>
       </c>
-      <c r="J59" s="10"/>
+      <c r="J59" s="20"/>
       <c r="K59" s="4">
         <v>100</v>
       </c>
@@ -7381,7 +7400,7 @@
       <c r="P59" s="6">
         <v>0</v>
       </c>
-      <c r="Q59" s="10"/>
+      <c r="Q59" s="20"/>
       <c r="R59" s="4">
         <v>100</v>
       </c>
@@ -7400,7 +7419,7 @@
       <c r="W59" s="6">
         <v>0</v>
       </c>
-      <c r="Y59" s="25"/>
+      <c r="Y59" s="15"/>
       <c r="Z59" s="4">
         <v>100</v>
       </c>
@@ -7424,7 +7443,7 @@
       <c r="B60" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="10"/>
+      <c r="C60" s="20"/>
       <c r="D60" s="4">
         <v>200</v>
       </c>
@@ -7443,7 +7462,7 @@
       <c r="I60" s="6">
         <v>0</v>
       </c>
-      <c r="J60" s="10"/>
+      <c r="J60" s="20"/>
       <c r="K60" s="4">
         <v>200</v>
       </c>
@@ -7462,7 +7481,7 @@
       <c r="P60" s="6">
         <v>0</v>
       </c>
-      <c r="Q60" s="10"/>
+      <c r="Q60" s="20"/>
       <c r="R60" s="4">
         <v>200</v>
       </c>
@@ -7481,7 +7500,7 @@
       <c r="W60" s="6">
         <v>0</v>
       </c>
-      <c r="Y60" s="25"/>
+      <c r="Y60" s="15"/>
       <c r="Z60" s="4">
         <v>200</v>
       </c>
@@ -7505,7 +7524,7 @@
       <c r="B61" t="s">
         <v>18</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="20"/>
       <c r="D61" s="4">
         <v>500</v>
       </c>
@@ -7524,7 +7543,7 @@
       <c r="I61" s="6">
         <v>0</v>
       </c>
-      <c r="J61" s="10"/>
+      <c r="J61" s="20"/>
       <c r="K61" s="4">
         <v>500</v>
       </c>
@@ -7543,7 +7562,7 @@
       <c r="P61" s="6">
         <v>0</v>
       </c>
-      <c r="Q61" s="10"/>
+      <c r="Q61" s="20"/>
       <c r="R61" s="4">
         <v>500</v>
       </c>
@@ -7562,7 +7581,7 @@
       <c r="W61" s="6">
         <v>0</v>
       </c>
-      <c r="Y61" s="25"/>
+      <c r="Y61" s="15"/>
       <c r="Z61" s="4">
         <v>500</v>
       </c>
@@ -7586,7 +7605,7 @@
       <c r="B62" t="s">
         <v>18</v>
       </c>
-      <c r="C62" s="10"/>
+      <c r="C62" s="20"/>
       <c r="D62" s="4">
         <v>1000</v>
       </c>
@@ -7605,7 +7624,7 @@
       <c r="I62" s="6">
         <v>0</v>
       </c>
-      <c r="J62" s="10"/>
+      <c r="J62" s="20"/>
       <c r="K62" s="4">
         <v>1000</v>
       </c>
@@ -7624,7 +7643,7 @@
       <c r="P62" s="6">
         <v>0</v>
       </c>
-      <c r="Q62" s="10"/>
+      <c r="Q62" s="20"/>
       <c r="R62" s="4">
         <v>1000</v>
       </c>
@@ -7643,7 +7662,7 @@
       <c r="W62" s="6">
         <v>0</v>
       </c>
-      <c r="Y62" s="25"/>
+      <c r="Y62" s="15"/>
       <c r="Z62" s="4">
         <v>1000</v>
       </c>
@@ -7667,7 +7686,7 @@
       <c r="B63" t="s">
         <v>19</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C63" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D63" s="4">
@@ -7688,7 +7707,7 @@
       <c r="I63" s="6">
         <v>0</v>
       </c>
-      <c r="J63" s="9" t="s">
+      <c r="J63" s="21" t="s">
         <v>97</v>
       </c>
       <c r="K63" s="4">
@@ -7709,7 +7728,7 @@
       <c r="P63" s="6">
         <v>0</v>
       </c>
-      <c r="Q63" s="9" t="s">
+      <c r="Q63" s="21" t="s">
         <v>73</v>
       </c>
       <c r="R63" s="4">
@@ -7730,7 +7749,7 @@
       <c r="W63" s="6">
         <v>0</v>
       </c>
-      <c r="Y63" s="26" t="s">
+      <c r="Y63" s="14" t="s">
         <v>53</v>
       </c>
       <c r="Z63" s="4">
@@ -7756,7 +7775,7 @@
       <c r="B64" t="s">
         <v>19</v>
       </c>
-      <c r="C64" s="10"/>
+      <c r="C64" s="20"/>
       <c r="D64" s="4">
         <v>100</v>
       </c>
@@ -7775,7 +7794,7 @@
       <c r="I64" s="6">
         <v>0</v>
       </c>
-      <c r="J64" s="10"/>
+      <c r="J64" s="20"/>
       <c r="K64" s="4">
         <v>100</v>
       </c>
@@ -7794,7 +7813,7 @@
       <c r="P64" s="6">
         <v>0</v>
       </c>
-      <c r="Q64" s="10"/>
+      <c r="Q64" s="20"/>
       <c r="R64" s="4">
         <v>100</v>
       </c>
@@ -7813,7 +7832,7 @@
       <c r="W64" s="6">
         <v>0</v>
       </c>
-      <c r="Y64" s="25"/>
+      <c r="Y64" s="15"/>
       <c r="Z64" s="4">
         <v>100</v>
       </c>
@@ -7837,7 +7856,7 @@
       <c r="B65" t="s">
         <v>19</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="20"/>
       <c r="D65" s="4">
         <v>200</v>
       </c>
@@ -7856,7 +7875,7 @@
       <c r="I65" s="6">
         <v>0</v>
       </c>
-      <c r="J65" s="10"/>
+      <c r="J65" s="20"/>
       <c r="K65" s="4">
         <v>200</v>
       </c>
@@ -7875,7 +7894,7 @@
       <c r="P65" s="6">
         <v>0</v>
       </c>
-      <c r="Q65" s="10"/>
+      <c r="Q65" s="20"/>
       <c r="R65" s="4">
         <v>200</v>
       </c>
@@ -7894,7 +7913,7 @@
       <c r="W65" s="6">
         <v>0</v>
       </c>
-      <c r="Y65" s="25"/>
+      <c r="Y65" s="15"/>
       <c r="Z65" s="4">
         <v>200</v>
       </c>
@@ -7918,7 +7937,7 @@
       <c r="B66" t="s">
         <v>19</v>
       </c>
-      <c r="C66" s="10"/>
+      <c r="C66" s="20"/>
       <c r="D66" s="4">
         <v>500</v>
       </c>
@@ -7937,7 +7956,7 @@
       <c r="I66" s="6">
         <v>0</v>
       </c>
-      <c r="J66" s="10"/>
+      <c r="J66" s="20"/>
       <c r="K66" s="4">
         <v>500</v>
       </c>
@@ -7956,7 +7975,7 @@
       <c r="P66" s="6">
         <v>0</v>
       </c>
-      <c r="Q66" s="10"/>
+      <c r="Q66" s="20"/>
       <c r="R66" s="4">
         <v>500</v>
       </c>
@@ -7975,7 +7994,7 @@
       <c r="W66" s="6">
         <v>0</v>
       </c>
-      <c r="Y66" s="25"/>
+      <c r="Y66" s="15"/>
       <c r="Z66" s="4">
         <v>500</v>
       </c>
@@ -7999,7 +8018,7 @@
       <c r="B67" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="20"/>
       <c r="D67" s="4">
         <v>1000</v>
       </c>
@@ -8018,7 +8037,7 @@
       <c r="I67" s="6">
         <v>0</v>
       </c>
-      <c r="J67" s="10"/>
+      <c r="J67" s="20"/>
       <c r="K67" s="4">
         <v>1000</v>
       </c>
@@ -8037,7 +8056,7 @@
       <c r="P67" s="6">
         <v>0</v>
       </c>
-      <c r="Q67" s="10"/>
+      <c r="Q67" s="20"/>
       <c r="R67" s="4">
         <v>1000</v>
       </c>
@@ -8056,7 +8075,7 @@
       <c r="W67" s="6">
         <v>0</v>
       </c>
-      <c r="Y67" s="25"/>
+      <c r="Y67" s="15"/>
       <c r="Z67" s="4">
         <v>1000</v>
       </c>
@@ -8080,7 +8099,7 @@
       <c r="B68" t="s">
         <v>20</v>
       </c>
-      <c r="C68" s="9" t="s">
+      <c r="C68" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D68" s="4">
@@ -8101,7 +8120,7 @@
       <c r="I68" s="6">
         <v>0</v>
       </c>
-      <c r="J68" s="9" t="s">
+      <c r="J68" s="21" t="s">
         <v>97</v>
       </c>
       <c r="K68" s="4">
@@ -8122,7 +8141,7 @@
       <c r="P68" s="6">
         <v>0</v>
       </c>
-      <c r="Q68" s="9" t="s">
+      <c r="Q68" s="21" t="s">
         <v>73</v>
       </c>
       <c r="R68" s="4">
@@ -8143,7 +8162,7 @@
       <c r="W68" s="6">
         <v>0</v>
       </c>
-      <c r="Y68" s="26" t="s">
+      <c r="Y68" s="14" t="s">
         <v>53</v>
       </c>
       <c r="Z68" s="4">
@@ -8169,7 +8188,7 @@
       <c r="B69" t="s">
         <v>20</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="20"/>
       <c r="D69" s="4">
         <v>100</v>
       </c>
@@ -8188,7 +8207,7 @@
       <c r="I69" s="6">
         <v>0</v>
       </c>
-      <c r="J69" s="10"/>
+      <c r="J69" s="20"/>
       <c r="K69" s="4">
         <v>100</v>
       </c>
@@ -8207,7 +8226,7 @@
       <c r="P69" s="6">
         <v>0</v>
       </c>
-      <c r="Q69" s="10"/>
+      <c r="Q69" s="20"/>
       <c r="R69" s="4">
         <v>100</v>
       </c>
@@ -8226,7 +8245,7 @@
       <c r="W69" s="6">
         <v>0</v>
       </c>
-      <c r="Y69" s="25"/>
+      <c r="Y69" s="15"/>
       <c r="Z69" s="4">
         <v>100</v>
       </c>
@@ -8250,7 +8269,7 @@
       <c r="B70" t="s">
         <v>20</v>
       </c>
-      <c r="C70" s="10"/>
+      <c r="C70" s="20"/>
       <c r="D70" s="4">
         <v>200</v>
       </c>
@@ -8269,7 +8288,7 @@
       <c r="I70" s="6">
         <v>0</v>
       </c>
-      <c r="J70" s="10"/>
+      <c r="J70" s="20"/>
       <c r="K70" s="4">
         <v>200</v>
       </c>
@@ -8288,7 +8307,7 @@
       <c r="P70" s="6">
         <v>0</v>
       </c>
-      <c r="Q70" s="10"/>
+      <c r="Q70" s="20"/>
       <c r="R70" s="4">
         <v>200</v>
       </c>
@@ -8307,7 +8326,7 @@
       <c r="W70" s="6">
         <v>0</v>
       </c>
-      <c r="Y70" s="25"/>
+      <c r="Y70" s="15"/>
       <c r="Z70" s="4">
         <v>200</v>
       </c>
@@ -8331,7 +8350,7 @@
       <c r="B71" t="s">
         <v>20</v>
       </c>
-      <c r="C71" s="10"/>
+      <c r="C71" s="20"/>
       <c r="D71" s="4">
         <v>500</v>
       </c>
@@ -8350,7 +8369,7 @@
       <c r="I71" s="6">
         <v>0</v>
       </c>
-      <c r="J71" s="10"/>
+      <c r="J71" s="20"/>
       <c r="K71" s="4">
         <v>500</v>
       </c>
@@ -8369,7 +8388,7 @@
       <c r="P71" s="6">
         <v>0</v>
       </c>
-      <c r="Q71" s="10"/>
+      <c r="Q71" s="20"/>
       <c r="R71" s="4">
         <v>500</v>
       </c>
@@ -8388,7 +8407,7 @@
       <c r="W71" s="6">
         <v>0</v>
       </c>
-      <c r="Y71" s="25"/>
+      <c r="Y71" s="15"/>
       <c r="Z71" s="4">
         <v>500</v>
       </c>
@@ -8412,7 +8431,7 @@
       <c r="B72" t="s">
         <v>20</v>
       </c>
-      <c r="C72" s="10"/>
+      <c r="C72" s="20"/>
       <c r="D72" s="4">
         <v>1000</v>
       </c>
@@ -8431,7 +8450,7 @@
       <c r="I72" s="6">
         <v>0</v>
       </c>
-      <c r="J72" s="10"/>
+      <c r="J72" s="20"/>
       <c r="K72" s="4">
         <v>1000</v>
       </c>
@@ -8450,7 +8469,7 @@
       <c r="P72" s="6">
         <v>0</v>
       </c>
-      <c r="Q72" s="10"/>
+      <c r="Q72" s="20"/>
       <c r="R72" s="4">
         <v>1000</v>
       </c>
@@ -8469,7 +8488,7 @@
       <c r="W72" s="6">
         <v>0</v>
       </c>
-      <c r="Y72" s="25"/>
+      <c r="Y72" s="15"/>
       <c r="Z72" s="4">
         <v>1000</v>
       </c>
@@ -8493,7 +8512,7 @@
       <c r="B73" t="s">
         <v>21</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D73" s="4">
@@ -8514,7 +8533,7 @@
       <c r="I73" s="6">
         <v>0</v>
       </c>
-      <c r="J73" s="9" t="s">
+      <c r="J73" s="21" t="s">
         <v>97</v>
       </c>
       <c r="K73" s="4">
@@ -8535,7 +8554,7 @@
       <c r="P73" s="6">
         <v>0</v>
       </c>
-      <c r="Q73" s="9" t="s">
+      <c r="Q73" s="21" t="s">
         <v>73</v>
       </c>
       <c r="R73" s="4">
@@ -8556,7 +8575,7 @@
       <c r="W73" s="6">
         <v>0</v>
       </c>
-      <c r="Y73" s="26" t="s">
+      <c r="Y73" s="14" t="s">
         <v>53</v>
       </c>
       <c r="Z73" s="4">
@@ -8582,7 +8601,7 @@
       <c r="B74" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="10"/>
+      <c r="C74" s="20"/>
       <c r="D74" s="4">
         <v>100</v>
       </c>
@@ -8601,7 +8620,7 @@
       <c r="I74" s="6">
         <v>0</v>
       </c>
-      <c r="J74" s="10"/>
+      <c r="J74" s="20"/>
       <c r="K74" s="4">
         <v>100</v>
       </c>
@@ -8620,7 +8639,7 @@
       <c r="P74" s="6">
         <v>0</v>
       </c>
-      <c r="Q74" s="10"/>
+      <c r="Q74" s="20"/>
       <c r="R74" s="4">
         <v>100</v>
       </c>
@@ -8639,7 +8658,7 @@
       <c r="W74" s="6">
         <v>0</v>
       </c>
-      <c r="Y74" s="25"/>
+      <c r="Y74" s="15"/>
       <c r="Z74" s="4">
         <v>100</v>
       </c>
@@ -8663,7 +8682,7 @@
       <c r="B75" t="s">
         <v>21</v>
       </c>
-      <c r="C75" s="10"/>
+      <c r="C75" s="20"/>
       <c r="D75" s="4">
         <v>200</v>
       </c>
@@ -8682,7 +8701,7 @@
       <c r="I75" s="6">
         <v>0</v>
       </c>
-      <c r="J75" s="10"/>
+      <c r="J75" s="20"/>
       <c r="K75" s="4">
         <v>200</v>
       </c>
@@ -8701,7 +8720,7 @@
       <c r="P75" s="6">
         <v>0</v>
       </c>
-      <c r="Q75" s="10"/>
+      <c r="Q75" s="20"/>
       <c r="R75" s="4">
         <v>200</v>
       </c>
@@ -8720,7 +8739,7 @@
       <c r="W75" s="6">
         <v>0</v>
       </c>
-      <c r="Y75" s="25"/>
+      <c r="Y75" s="15"/>
       <c r="Z75" s="4">
         <v>200</v>
       </c>
@@ -8744,7 +8763,7 @@
       <c r="B76" t="s">
         <v>21</v>
       </c>
-      <c r="C76" s="10"/>
+      <c r="C76" s="20"/>
       <c r="D76" s="4">
         <v>500</v>
       </c>
@@ -8763,7 +8782,7 @@
       <c r="I76" s="6">
         <v>0</v>
       </c>
-      <c r="J76" s="10"/>
+      <c r="J76" s="20"/>
       <c r="K76" s="4">
         <v>500</v>
       </c>
@@ -8782,7 +8801,7 @@
       <c r="P76" s="6">
         <v>0</v>
       </c>
-      <c r="Q76" s="10"/>
+      <c r="Q76" s="20"/>
       <c r="R76" s="4">
         <v>500</v>
       </c>
@@ -8801,7 +8820,7 @@
       <c r="W76" s="6">
         <v>0</v>
       </c>
-      <c r="Y76" s="25"/>
+      <c r="Y76" s="15"/>
       <c r="Z76" s="4">
         <v>500</v>
       </c>
@@ -8825,7 +8844,7 @@
       <c r="B77" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="10"/>
+      <c r="C77" s="20"/>
       <c r="D77" s="4">
         <v>1000</v>
       </c>
@@ -8844,7 +8863,7 @@
       <c r="I77" s="6">
         <v>0</v>
       </c>
-      <c r="J77" s="10"/>
+      <c r="J77" s="20"/>
       <c r="K77" s="4">
         <v>1000</v>
       </c>
@@ -8863,7 +8882,7 @@
       <c r="P77" s="6">
         <v>0</v>
       </c>
-      <c r="Q77" s="10"/>
+      <c r="Q77" s="20"/>
       <c r="R77" s="4">
         <v>1000</v>
       </c>
@@ -8882,7 +8901,7 @@
       <c r="W77" s="6">
         <v>0</v>
       </c>
-      <c r="Y77" s="25"/>
+      <c r="Y77" s="15"/>
       <c r="Z77" s="4">
         <v>1000</v>
       </c>
@@ -8906,7 +8925,7 @@
       <c r="B78" t="s">
         <v>22</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D78" s="4">
@@ -8927,7 +8946,7 @@
       <c r="I78" s="6">
         <v>0</v>
       </c>
-      <c r="J78" s="9" t="s">
+      <c r="J78" s="21" t="s">
         <v>97</v>
       </c>
       <c r="K78" s="4">
@@ -8948,7 +8967,7 @@
       <c r="P78" s="6">
         <v>0</v>
       </c>
-      <c r="Q78" s="9" t="s">
+      <c r="Q78" s="21" t="s">
         <v>73</v>
       </c>
       <c r="R78" s="4">
@@ -8969,7 +8988,7 @@
       <c r="W78" s="6">
         <v>0</v>
       </c>
-      <c r="Y78" s="26" t="s">
+      <c r="Y78" s="14" t="s">
         <v>53</v>
       </c>
       <c r="Z78" s="4">
@@ -8995,7 +9014,7 @@
       <c r="B79" t="s">
         <v>22</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="20"/>
       <c r="D79" s="4">
         <v>100</v>
       </c>
@@ -9014,7 +9033,7 @@
       <c r="I79" s="6">
         <v>0</v>
       </c>
-      <c r="J79" s="10"/>
+      <c r="J79" s="20"/>
       <c r="K79" s="4">
         <v>100</v>
       </c>
@@ -9033,7 +9052,7 @@
       <c r="P79" s="6">
         <v>0</v>
       </c>
-      <c r="Q79" s="10"/>
+      <c r="Q79" s="20"/>
       <c r="R79" s="4">
         <v>100</v>
       </c>
@@ -9052,7 +9071,7 @@
       <c r="W79" s="6">
         <v>0</v>
       </c>
-      <c r="Y79" s="25"/>
+      <c r="Y79" s="15"/>
       <c r="Z79" s="4">
         <v>100</v>
       </c>
@@ -9076,7 +9095,7 @@
       <c r="B80" t="s">
         <v>22</v>
       </c>
-      <c r="C80" s="10"/>
+      <c r="C80" s="20"/>
       <c r="D80" s="4">
         <v>200</v>
       </c>
@@ -9095,7 +9114,7 @@
       <c r="I80" s="6">
         <v>0</v>
       </c>
-      <c r="J80" s="10"/>
+      <c r="J80" s="20"/>
       <c r="K80" s="4">
         <v>200</v>
       </c>
@@ -9114,7 +9133,7 @@
       <c r="P80" s="6">
         <v>0</v>
       </c>
-      <c r="Q80" s="10"/>
+      <c r="Q80" s="20"/>
       <c r="R80" s="4">
         <v>200</v>
       </c>
@@ -9133,7 +9152,7 @@
       <c r="W80" s="6">
         <v>0</v>
       </c>
-      <c r="Y80" s="25"/>
+      <c r="Y80" s="15"/>
       <c r="Z80" s="4">
         <v>200</v>
       </c>
@@ -9157,7 +9176,7 @@
       <c r="B81" t="s">
         <v>22</v>
       </c>
-      <c r="C81" s="10"/>
+      <c r="C81" s="20"/>
       <c r="D81" s="4">
         <v>500</v>
       </c>
@@ -9176,7 +9195,7 @@
       <c r="I81" s="6">
         <v>0</v>
       </c>
-      <c r="J81" s="10"/>
+      <c r="J81" s="20"/>
       <c r="K81" s="4">
         <v>500</v>
       </c>
@@ -9195,7 +9214,7 @@
       <c r="P81" s="6">
         <v>0</v>
       </c>
-      <c r="Q81" s="10"/>
+      <c r="Q81" s="20"/>
       <c r="R81" s="4">
         <v>500</v>
       </c>
@@ -9214,7 +9233,7 @@
       <c r="W81" s="6">
         <v>0</v>
       </c>
-      <c r="Y81" s="25"/>
+      <c r="Y81" s="15"/>
       <c r="Z81" s="4">
         <v>500</v>
       </c>
@@ -9238,7 +9257,7 @@
       <c r="B82" t="s">
         <v>22</v>
       </c>
-      <c r="C82" s="10"/>
+      <c r="C82" s="20"/>
       <c r="D82" s="4">
         <v>1000</v>
       </c>
@@ -9257,7 +9276,7 @@
       <c r="I82" s="6">
         <v>0</v>
       </c>
-      <c r="J82" s="10"/>
+      <c r="J82" s="20"/>
       <c r="K82" s="4">
         <v>1000</v>
       </c>
@@ -9276,7 +9295,7 @@
       <c r="P82" s="6">
         <v>0</v>
       </c>
-      <c r="Q82" s="10"/>
+      <c r="Q82" s="20"/>
       <c r="R82" s="4">
         <v>1000</v>
       </c>
@@ -9295,7 +9314,7 @@
       <c r="W82" s="6">
         <v>0</v>
       </c>
-      <c r="Y82" s="25"/>
+      <c r="Y82" s="15"/>
       <c r="Z82" s="4">
         <v>1000</v>
       </c>
@@ -9319,7 +9338,7 @@
       <c r="B83" t="s">
         <v>23</v>
       </c>
-      <c r="C83" s="9" t="s">
+      <c r="C83" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D83" s="4">
@@ -9340,7 +9359,7 @@
       <c r="I83" s="6">
         <v>0</v>
       </c>
-      <c r="J83" s="9" t="s">
+      <c r="J83" s="21" t="s">
         <v>97</v>
       </c>
       <c r="K83" s="4">
@@ -9361,7 +9380,7 @@
       <c r="P83" s="6">
         <v>0</v>
       </c>
-      <c r="Q83" s="9" t="s">
+      <c r="Q83" s="21" t="s">
         <v>73</v>
       </c>
       <c r="R83" s="4">
@@ -9382,7 +9401,7 @@
       <c r="W83" s="6">
         <v>0</v>
       </c>
-      <c r="Y83" s="26" t="s">
+      <c r="Y83" s="14" t="s">
         <v>53</v>
       </c>
       <c r="Z83" s="4">
@@ -9408,7 +9427,7 @@
       <c r="B84" t="s">
         <v>23</v>
       </c>
-      <c r="C84" s="10"/>
+      <c r="C84" s="20"/>
       <c r="D84" s="4">
         <v>100</v>
       </c>
@@ -9427,7 +9446,7 @@
       <c r="I84" s="6">
         <v>0</v>
       </c>
-      <c r="J84" s="10"/>
+      <c r="J84" s="20"/>
       <c r="K84" s="4">
         <v>100</v>
       </c>
@@ -9446,7 +9465,7 @@
       <c r="P84" s="6">
         <v>0</v>
       </c>
-      <c r="Q84" s="10"/>
+      <c r="Q84" s="20"/>
       <c r="R84" s="4">
         <v>100</v>
       </c>
@@ -9465,7 +9484,7 @@
       <c r="W84" s="6">
         <v>0</v>
       </c>
-      <c r="Y84" s="25"/>
+      <c r="Y84" s="15"/>
       <c r="Z84" s="4">
         <v>100</v>
       </c>
@@ -9489,7 +9508,7 @@
       <c r="B85" t="s">
         <v>23</v>
       </c>
-      <c r="C85" s="10"/>
+      <c r="C85" s="20"/>
       <c r="D85" s="4">
         <v>200</v>
       </c>
@@ -9508,7 +9527,7 @@
       <c r="I85" s="6">
         <v>0</v>
       </c>
-      <c r="J85" s="10"/>
+      <c r="J85" s="20"/>
       <c r="K85" s="4">
         <v>200</v>
       </c>
@@ -9527,7 +9546,7 @@
       <c r="P85" s="6">
         <v>0</v>
       </c>
-      <c r="Q85" s="10"/>
+      <c r="Q85" s="20"/>
       <c r="R85" s="4">
         <v>200</v>
       </c>
@@ -9546,7 +9565,7 @@
       <c r="W85" s="6">
         <v>0</v>
       </c>
-      <c r="Y85" s="25"/>
+      <c r="Y85" s="15"/>
       <c r="Z85" s="4">
         <v>200</v>
       </c>
@@ -9570,7 +9589,7 @@
       <c r="B86" t="s">
         <v>23</v>
       </c>
-      <c r="C86" s="10"/>
+      <c r="C86" s="20"/>
       <c r="D86" s="4">
         <v>500</v>
       </c>
@@ -9589,7 +9608,7 @@
       <c r="I86" s="6">
         <v>0</v>
       </c>
-      <c r="J86" s="10"/>
+      <c r="J86" s="20"/>
       <c r="K86" s="4">
         <v>500</v>
       </c>
@@ -9608,7 +9627,7 @@
       <c r="P86" s="6">
         <v>0</v>
       </c>
-      <c r="Q86" s="10"/>
+      <c r="Q86" s="20"/>
       <c r="R86" s="4">
         <v>500</v>
       </c>
@@ -9627,7 +9646,7 @@
       <c r="W86" s="6">
         <v>0</v>
       </c>
-      <c r="Y86" s="25"/>
+      <c r="Y86" s="15"/>
       <c r="Z86" s="4">
         <v>500</v>
       </c>
@@ -9651,7 +9670,7 @@
       <c r="B87" t="s">
         <v>23</v>
       </c>
-      <c r="C87" s="10"/>
+      <c r="C87" s="20"/>
       <c r="D87" s="4">
         <v>1000</v>
       </c>
@@ -9670,7 +9689,7 @@
       <c r="I87" s="6">
         <v>0</v>
       </c>
-      <c r="J87" s="10"/>
+      <c r="J87" s="20"/>
       <c r="K87" s="4">
         <v>1000</v>
       </c>
@@ -9689,7 +9708,7 @@
       <c r="P87" s="6">
         <v>0</v>
       </c>
-      <c r="Q87" s="10"/>
+      <c r="Q87" s="20"/>
       <c r="R87" s="4">
         <v>1000</v>
       </c>
@@ -9708,7 +9727,7 @@
       <c r="W87" s="6">
         <v>0</v>
       </c>
-      <c r="Y87" s="25"/>
+      <c r="Y87" s="15"/>
       <c r="Z87" s="4">
         <v>1000</v>
       </c>
@@ -9732,7 +9751,7 @@
       <c r="B88" t="s">
         <v>24</v>
       </c>
-      <c r="C88" s="9" t="s">
+      <c r="C88" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D88" s="4">
@@ -9753,7 +9772,7 @@
       <c r="I88" s="6">
         <v>0</v>
       </c>
-      <c r="J88" s="9" t="s">
+      <c r="J88" s="21" t="s">
         <v>97</v>
       </c>
       <c r="K88" s="4">
@@ -9774,7 +9793,7 @@
       <c r="P88" s="6">
         <v>0</v>
       </c>
-      <c r="Q88" s="9" t="s">
+      <c r="Q88" s="21" t="s">
         <v>73</v>
       </c>
       <c r="R88" s="4">
@@ -9795,7 +9814,7 @@
       <c r="W88" s="6">
         <v>0</v>
       </c>
-      <c r="Y88" s="26" t="s">
+      <c r="Y88" s="14" t="s">
         <v>53</v>
       </c>
       <c r="Z88" s="4">
@@ -9821,7 +9840,7 @@
       <c r="B89" t="s">
         <v>24</v>
       </c>
-      <c r="C89" s="10"/>
+      <c r="C89" s="20"/>
       <c r="D89" s="4">
         <v>100</v>
       </c>
@@ -9840,7 +9859,7 @@
       <c r="I89" s="6">
         <v>0</v>
       </c>
-      <c r="J89" s="10"/>
+      <c r="J89" s="20"/>
       <c r="K89" s="4">
         <v>100</v>
       </c>
@@ -9859,7 +9878,7 @@
       <c r="P89" s="6">
         <v>0</v>
       </c>
-      <c r="Q89" s="10"/>
+      <c r="Q89" s="20"/>
       <c r="R89" s="4">
         <v>100</v>
       </c>
@@ -9878,7 +9897,7 @@
       <c r="W89" s="6">
         <v>0</v>
       </c>
-      <c r="Y89" s="25"/>
+      <c r="Y89" s="15"/>
       <c r="Z89" s="4">
         <v>100</v>
       </c>
@@ -9902,7 +9921,7 @@
       <c r="B90" t="s">
         <v>24</v>
       </c>
-      <c r="C90" s="10"/>
+      <c r="C90" s="20"/>
       <c r="D90" s="4">
         <v>200</v>
       </c>
@@ -9921,7 +9940,7 @@
       <c r="I90" s="6">
         <v>0</v>
       </c>
-      <c r="J90" s="10"/>
+      <c r="J90" s="20"/>
       <c r="K90" s="4">
         <v>200</v>
       </c>
@@ -9940,7 +9959,7 @@
       <c r="P90" s="6">
         <v>0</v>
       </c>
-      <c r="Q90" s="10"/>
+      <c r="Q90" s="20"/>
       <c r="R90" s="4">
         <v>200</v>
       </c>
@@ -9959,7 +9978,7 @@
       <c r="W90" s="6">
         <v>0</v>
       </c>
-      <c r="Y90" s="25"/>
+      <c r="Y90" s="15"/>
       <c r="Z90" s="4">
         <v>200</v>
       </c>
@@ -9983,7 +10002,7 @@
       <c r="B91" t="s">
         <v>24</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="20"/>
       <c r="D91" s="4">
         <v>500</v>
       </c>
@@ -10002,7 +10021,7 @@
       <c r="I91" s="6">
         <v>0</v>
       </c>
-      <c r="J91" s="10"/>
+      <c r="J91" s="20"/>
       <c r="K91" s="4">
         <v>500</v>
       </c>
@@ -10021,7 +10040,7 @@
       <c r="P91" s="6">
         <v>0</v>
       </c>
-      <c r="Q91" s="10"/>
+      <c r="Q91" s="20"/>
       <c r="R91" s="4">
         <v>500</v>
       </c>
@@ -10040,7 +10059,7 @@
       <c r="W91" s="6">
         <v>0</v>
       </c>
-      <c r="Y91" s="25"/>
+      <c r="Y91" s="15"/>
       <c r="Z91" s="4">
         <v>500</v>
       </c>
@@ -10064,7 +10083,7 @@
       <c r="B92" t="s">
         <v>24</v>
       </c>
-      <c r="C92" s="10"/>
+      <c r="C92" s="20"/>
       <c r="D92" s="4">
         <v>1000</v>
       </c>
@@ -10083,7 +10102,7 @@
       <c r="I92" s="6">
         <v>0</v>
       </c>
-      <c r="J92" s="10"/>
+      <c r="J92" s="20"/>
       <c r="K92" s="4">
         <v>1000</v>
       </c>
@@ -10102,7 +10121,7 @@
       <c r="P92" s="6">
         <v>0</v>
       </c>
-      <c r="Q92" s="10"/>
+      <c r="Q92" s="20"/>
       <c r="R92" s="4">
         <v>1000</v>
       </c>
@@ -10121,7 +10140,7 @@
       <c r="W92" s="6">
         <v>0</v>
       </c>
-      <c r="Y92" s="25"/>
+      <c r="Y92" s="15"/>
       <c r="Z92" s="4">
         <v>1000</v>
       </c>
@@ -10145,7 +10164,7 @@
       <c r="B93" t="s">
         <v>25</v>
       </c>
-      <c r="C93" s="9" t="s">
+      <c r="C93" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D93" s="4">
@@ -10166,7 +10185,7 @@
       <c r="I93" s="6">
         <v>0</v>
       </c>
-      <c r="J93" s="9" t="s">
+      <c r="J93" s="21" t="s">
         <v>97</v>
       </c>
       <c r="K93" s="4">
@@ -10187,7 +10206,7 @@
       <c r="P93" s="6">
         <v>0</v>
       </c>
-      <c r="Q93" s="9" t="s">
+      <c r="Q93" s="21" t="s">
         <v>73</v>
       </c>
       <c r="R93" s="4">
@@ -10208,7 +10227,7 @@
       <c r="W93" s="6">
         <v>0</v>
       </c>
-      <c r="Y93" s="26" t="s">
+      <c r="Y93" s="14" t="s">
         <v>53</v>
       </c>
       <c r="Z93" s="4">
@@ -10234,7 +10253,7 @@
       <c r="B94" t="s">
         <v>25</v>
       </c>
-      <c r="C94" s="10"/>
+      <c r="C94" s="20"/>
       <c r="D94" s="4">
         <v>100</v>
       </c>
@@ -10253,7 +10272,7 @@
       <c r="I94" s="6">
         <v>0</v>
       </c>
-      <c r="J94" s="10"/>
+      <c r="J94" s="20"/>
       <c r="K94" s="4">
         <v>100</v>
       </c>
@@ -10272,7 +10291,7 @@
       <c r="P94" s="6">
         <v>0</v>
       </c>
-      <c r="Q94" s="10"/>
+      <c r="Q94" s="20"/>
       <c r="R94" s="4">
         <v>100</v>
       </c>
@@ -10291,7 +10310,7 @@
       <c r="W94" s="6">
         <v>0</v>
       </c>
-      <c r="Y94" s="25"/>
+      <c r="Y94" s="15"/>
       <c r="Z94" s="4">
         <v>100</v>
       </c>
@@ -10315,7 +10334,7 @@
       <c r="B95" t="s">
         <v>25</v>
       </c>
-      <c r="C95" s="10"/>
+      <c r="C95" s="20"/>
       <c r="D95" s="4">
         <v>200</v>
       </c>
@@ -10334,7 +10353,7 @@
       <c r="I95" s="6">
         <v>0</v>
       </c>
-      <c r="J95" s="10"/>
+      <c r="J95" s="20"/>
       <c r="K95" s="4">
         <v>200</v>
       </c>
@@ -10353,7 +10372,7 @@
       <c r="P95" s="6">
         <v>0</v>
       </c>
-      <c r="Q95" s="10"/>
+      <c r="Q95" s="20"/>
       <c r="R95" s="4">
         <v>200</v>
       </c>
@@ -10372,7 +10391,7 @@
       <c r="W95" s="6">
         <v>0</v>
       </c>
-      <c r="Y95" s="25"/>
+      <c r="Y95" s="15"/>
       <c r="Z95" s="4">
         <v>200</v>
       </c>
@@ -10396,7 +10415,7 @@
       <c r="B96" t="s">
         <v>25</v>
       </c>
-      <c r="C96" s="10"/>
+      <c r="C96" s="20"/>
       <c r="D96" s="4">
         <v>500</v>
       </c>
@@ -10415,7 +10434,7 @@
       <c r="I96" s="6">
         <v>0</v>
       </c>
-      <c r="J96" s="10"/>
+      <c r="J96" s="20"/>
       <c r="K96" s="4">
         <v>500</v>
       </c>
@@ -10434,7 +10453,7 @@
       <c r="P96" s="6">
         <v>0</v>
       </c>
-      <c r="Q96" s="10"/>
+      <c r="Q96" s="20"/>
       <c r="R96" s="4">
         <v>500</v>
       </c>
@@ -10453,7 +10472,7 @@
       <c r="W96" s="6">
         <v>0</v>
       </c>
-      <c r="Y96" s="25"/>
+      <c r="Y96" s="15"/>
       <c r="Z96" s="4">
         <v>500</v>
       </c>
@@ -10477,7 +10496,7 @@
       <c r="B97" t="s">
         <v>25</v>
       </c>
-      <c r="C97" s="10"/>
+      <c r="C97" s="20"/>
       <c r="D97" s="4">
         <v>1000</v>
       </c>
@@ -10496,7 +10515,7 @@
       <c r="I97" s="6">
         <v>0</v>
       </c>
-      <c r="J97" s="10"/>
+      <c r="J97" s="20"/>
       <c r="K97" s="4">
         <v>1000</v>
       </c>
@@ -10515,7 +10534,7 @@
       <c r="P97" s="6">
         <v>0</v>
       </c>
-      <c r="Q97" s="10"/>
+      <c r="Q97" s="20"/>
       <c r="R97" s="4">
         <v>1000</v>
       </c>
@@ -10534,7 +10553,7 @@
       <c r="W97" s="6">
         <v>0</v>
       </c>
-      <c r="Y97" s="25"/>
+      <c r="Y97" s="15"/>
       <c r="Z97" s="4">
         <v>1000</v>
       </c>
@@ -10558,7 +10577,7 @@
       <c r="B98" t="s">
         <v>26</v>
       </c>
-      <c r="C98" s="9" t="s">
+      <c r="C98" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D98" s="4">
@@ -10579,7 +10598,7 @@
       <c r="I98" s="6">
         <v>0</v>
       </c>
-      <c r="J98" s="9" t="s">
+      <c r="J98" s="21" t="s">
         <v>97</v>
       </c>
       <c r="K98" s="4">
@@ -10600,7 +10619,7 @@
       <c r="P98" s="6">
         <v>0</v>
       </c>
-      <c r="Q98" s="9" t="s">
+      <c r="Q98" s="21" t="s">
         <v>73</v>
       </c>
       <c r="R98" s="4">
@@ -10621,7 +10640,7 @@
       <c r="W98" s="6">
         <v>0</v>
       </c>
-      <c r="Y98" s="26" t="s">
+      <c r="Y98" s="14" t="s">
         <v>53</v>
       </c>
       <c r="Z98" s="4">
@@ -10647,7 +10666,7 @@
       <c r="B99" t="s">
         <v>26</v>
       </c>
-      <c r="C99" s="10"/>
+      <c r="C99" s="20"/>
       <c r="D99" s="4">
         <v>100</v>
       </c>
@@ -10666,7 +10685,7 @@
       <c r="I99" s="6">
         <v>0</v>
       </c>
-      <c r="J99" s="10"/>
+      <c r="J99" s="20"/>
       <c r="K99" s="4">
         <v>100</v>
       </c>
@@ -10685,7 +10704,7 @@
       <c r="P99" s="6">
         <v>0</v>
       </c>
-      <c r="Q99" s="10"/>
+      <c r="Q99" s="20"/>
       <c r="R99" s="4">
         <v>100</v>
       </c>
@@ -10704,7 +10723,7 @@
       <c r="W99" s="6">
         <v>0</v>
       </c>
-      <c r="Y99" s="25"/>
+      <c r="Y99" s="15"/>
       <c r="Z99" s="4">
         <v>100</v>
       </c>
@@ -10728,7 +10747,7 @@
       <c r="B100" t="s">
         <v>26</v>
       </c>
-      <c r="C100" s="10"/>
+      <c r="C100" s="20"/>
       <c r="D100" s="4">
         <v>200</v>
       </c>
@@ -10747,7 +10766,7 @@
       <c r="I100" s="6">
         <v>0</v>
       </c>
-      <c r="J100" s="10"/>
+      <c r="J100" s="20"/>
       <c r="K100" s="4">
         <v>200</v>
       </c>
@@ -10766,7 +10785,7 @@
       <c r="P100" s="6">
         <v>0</v>
       </c>
-      <c r="Q100" s="10"/>
+      <c r="Q100" s="20"/>
       <c r="R100" s="4">
         <v>200</v>
       </c>
@@ -10785,7 +10804,7 @@
       <c r="W100" s="6">
         <v>0</v>
       </c>
-      <c r="Y100" s="25"/>
+      <c r="Y100" s="15"/>
       <c r="Z100" s="4">
         <v>200</v>
       </c>
@@ -10809,7 +10828,7 @@
       <c r="B101" t="s">
         <v>26</v>
       </c>
-      <c r="C101" s="10"/>
+      <c r="C101" s="20"/>
       <c r="D101" s="4">
         <v>500</v>
       </c>
@@ -10828,7 +10847,7 @@
       <c r="I101" s="6">
         <v>0</v>
       </c>
-      <c r="J101" s="10"/>
+      <c r="J101" s="20"/>
       <c r="K101" s="4">
         <v>500</v>
       </c>
@@ -10847,7 +10866,7 @@
       <c r="P101" s="6">
         <v>0</v>
       </c>
-      <c r="Q101" s="10"/>
+      <c r="Q101" s="20"/>
       <c r="R101" s="4">
         <v>500</v>
       </c>
@@ -10866,7 +10885,7 @@
       <c r="W101" s="6">
         <v>0</v>
       </c>
-      <c r="Y101" s="25"/>
+      <c r="Y101" s="15"/>
       <c r="Z101" s="4">
         <v>500</v>
       </c>
@@ -10890,7 +10909,7 @@
       <c r="B102" t="s">
         <v>26</v>
       </c>
-      <c r="C102" s="10"/>
+      <c r="C102" s="20"/>
       <c r="D102" s="4">
         <v>1000</v>
       </c>
@@ -10909,7 +10928,7 @@
       <c r="I102" s="6">
         <v>0</v>
       </c>
-      <c r="J102" s="10"/>
+      <c r="J102" s="20"/>
       <c r="K102" s="4">
         <v>1000</v>
       </c>
@@ -10928,7 +10947,7 @@
       <c r="P102" s="6">
         <v>0</v>
       </c>
-      <c r="Q102" s="10"/>
+      <c r="Q102" s="20"/>
       <c r="R102" s="4">
         <v>1000</v>
       </c>
@@ -10947,7 +10966,7 @@
       <c r="W102" s="6">
         <v>0</v>
       </c>
-      <c r="Y102" s="25"/>
+      <c r="Y102" s="15"/>
       <c r="Z102" s="4">
         <v>1000</v>
       </c>
@@ -10971,7 +10990,7 @@
       <c r="B103" t="s">
         <v>27</v>
       </c>
-      <c r="C103" s="9" t="s">
+      <c r="C103" s="21" t="s">
         <v>54</v>
       </c>
       <c r="D103" s="4">
@@ -10992,7 +11011,7 @@
       <c r="I103" s="6">
         <v>0</v>
       </c>
-      <c r="J103" s="9" t="s">
+      <c r="J103" s="21" t="s">
         <v>98</v>
       </c>
       <c r="K103" s="4">
@@ -11013,7 +11032,7 @@
       <c r="P103" s="6">
         <v>0</v>
       </c>
-      <c r="Q103" s="9" t="s">
+      <c r="Q103" s="21" t="s">
         <v>74</v>
       </c>
       <c r="R103" s="4">
@@ -11034,7 +11053,7 @@
       <c r="W103" s="6">
         <v>0</v>
       </c>
-      <c r="Y103" s="26" t="s">
+      <c r="Y103" s="14" t="s">
         <v>54</v>
       </c>
       <c r="Z103" s="4">
@@ -11060,7 +11079,7 @@
       <c r="B104" t="s">
         <v>27</v>
       </c>
-      <c r="C104" s="10"/>
+      <c r="C104" s="20"/>
       <c r="D104" s="4">
         <v>100</v>
       </c>
@@ -11079,7 +11098,7 @@
       <c r="I104" s="6">
         <v>0</v>
       </c>
-      <c r="J104" s="10"/>
+      <c r="J104" s="20"/>
       <c r="K104" s="4">
         <v>100</v>
       </c>
@@ -11098,7 +11117,7 @@
       <c r="P104" s="6">
         <v>0</v>
       </c>
-      <c r="Q104" s="10"/>
+      <c r="Q104" s="20"/>
       <c r="R104" s="4">
         <v>100</v>
       </c>
@@ -11117,7 +11136,7 @@
       <c r="W104" s="6">
         <v>0</v>
       </c>
-      <c r="Y104" s="25"/>
+      <c r="Y104" s="15"/>
       <c r="Z104" s="4">
         <v>100</v>
       </c>
@@ -11141,7 +11160,7 @@
       <c r="B105" t="s">
         <v>27</v>
       </c>
-      <c r="C105" s="10"/>
+      <c r="C105" s="20"/>
       <c r="D105" s="4">
         <v>200</v>
       </c>
@@ -11160,7 +11179,7 @@
       <c r="I105" s="6">
         <v>0</v>
       </c>
-      <c r="J105" s="10"/>
+      <c r="J105" s="20"/>
       <c r="K105" s="4">
         <v>200</v>
       </c>
@@ -11179,7 +11198,7 @@
       <c r="P105" s="6">
         <v>0</v>
       </c>
-      <c r="Q105" s="10"/>
+      <c r="Q105" s="20"/>
       <c r="R105" s="4">
         <v>200</v>
       </c>
@@ -11198,7 +11217,7 @@
       <c r="W105" s="6">
         <v>0</v>
       </c>
-      <c r="Y105" s="25"/>
+      <c r="Y105" s="15"/>
       <c r="Z105" s="4">
         <v>200</v>
       </c>
@@ -11222,7 +11241,7 @@
       <c r="B106" t="s">
         <v>27</v>
       </c>
-      <c r="C106" s="10"/>
+      <c r="C106" s="20"/>
       <c r="D106" s="4">
         <v>500</v>
       </c>
@@ -11241,7 +11260,7 @@
       <c r="I106" s="6">
         <v>0</v>
       </c>
-      <c r="J106" s="10"/>
+      <c r="J106" s="20"/>
       <c r="K106" s="4">
         <v>500</v>
       </c>
@@ -11260,7 +11279,7 @@
       <c r="P106" s="6">
         <v>0</v>
       </c>
-      <c r="Q106" s="10"/>
+      <c r="Q106" s="20"/>
       <c r="R106" s="4">
         <v>500</v>
       </c>
@@ -11279,7 +11298,7 @@
       <c r="W106" s="6">
         <v>0</v>
       </c>
-      <c r="Y106" s="25"/>
+      <c r="Y106" s="15"/>
       <c r="Z106" s="4">
         <v>500</v>
       </c>
@@ -11303,7 +11322,7 @@
       <c r="B107" t="s">
         <v>27</v>
       </c>
-      <c r="C107" s="10"/>
+      <c r="C107" s="20"/>
       <c r="D107" s="4">
         <v>1000</v>
       </c>
@@ -11322,7 +11341,7 @@
       <c r="I107" s="6">
         <v>0</v>
       </c>
-      <c r="J107" s="10"/>
+      <c r="J107" s="20"/>
       <c r="K107" s="4">
         <v>1000</v>
       </c>
@@ -11341,7 +11360,7 @@
       <c r="P107" s="6">
         <v>0</v>
       </c>
-      <c r="Q107" s="10"/>
+      <c r="Q107" s="20"/>
       <c r="R107" s="4">
         <v>1000</v>
       </c>
@@ -11360,7 +11379,7 @@
       <c r="W107" s="6">
         <v>0</v>
       </c>
-      <c r="Y107" s="25"/>
+      <c r="Y107" s="15"/>
       <c r="Z107" s="4">
         <v>1000</v>
       </c>
@@ -11384,7 +11403,7 @@
       <c r="B108" t="s">
         <v>28</v>
       </c>
-      <c r="C108" s="9" t="s">
+      <c r="C108" s="21" t="s">
         <v>99</v>
       </c>
       <c r="D108" s="4">
@@ -11405,7 +11424,7 @@
       <c r="I108" s="6">
         <v>0</v>
       </c>
-      <c r="J108" s="9" t="s">
+      <c r="J108" s="21" t="s">
         <v>100</v>
       </c>
       <c r="K108" s="4">
@@ -11426,7 +11445,7 @@
       <c r="P108" s="6">
         <v>0</v>
       </c>
-      <c r="Q108" s="9" t="s">
+      <c r="Q108" s="21" t="s">
         <v>75</v>
       </c>
       <c r="R108" s="4">
@@ -11447,7 +11466,7 @@
       <c r="W108" s="6">
         <v>0</v>
       </c>
-      <c r="Y108" s="26" t="s">
+      <c r="Y108" s="14" t="s">
         <v>99</v>
       </c>
       <c r="Z108" s="4">
@@ -11473,7 +11492,7 @@
       <c r="B109" t="s">
         <v>28</v>
       </c>
-      <c r="C109" s="10"/>
+      <c r="C109" s="20"/>
       <c r="D109" s="4">
         <v>100</v>
       </c>
@@ -11492,7 +11511,7 @@
       <c r="I109" s="6">
         <v>0</v>
       </c>
-      <c r="J109" s="10"/>
+      <c r="J109" s="20"/>
       <c r="K109" s="4">
         <v>100</v>
       </c>
@@ -11511,7 +11530,7 @@
       <c r="P109" s="6">
         <v>0</v>
       </c>
-      <c r="Q109" s="10"/>
+      <c r="Q109" s="20"/>
       <c r="R109" s="4">
         <v>100</v>
       </c>
@@ -11530,7 +11549,7 @@
       <c r="W109" s="6">
         <v>0</v>
       </c>
-      <c r="Y109" s="25"/>
+      <c r="Y109" s="15"/>
       <c r="Z109" s="4">
         <v>100</v>
       </c>
@@ -11554,7 +11573,7 @@
       <c r="B110" t="s">
         <v>28</v>
       </c>
-      <c r="C110" s="10"/>
+      <c r="C110" s="20"/>
       <c r="D110" s="4">
         <v>200</v>
       </c>
@@ -11573,7 +11592,7 @@
       <c r="I110" s="6">
         <v>0</v>
       </c>
-      <c r="J110" s="10"/>
+      <c r="J110" s="20"/>
       <c r="K110" s="4">
         <v>200</v>
       </c>
@@ -11592,7 +11611,7 @@
       <c r="P110" s="6">
         <v>0</v>
       </c>
-      <c r="Q110" s="10"/>
+      <c r="Q110" s="20"/>
       <c r="R110" s="4">
         <v>200</v>
       </c>
@@ -11611,7 +11630,7 @@
       <c r="W110" s="6">
         <v>0</v>
       </c>
-      <c r="Y110" s="25"/>
+      <c r="Y110" s="15"/>
       <c r="Z110" s="4">
         <v>200</v>
       </c>
@@ -11635,7 +11654,7 @@
       <c r="B111" t="s">
         <v>28</v>
       </c>
-      <c r="C111" s="10"/>
+      <c r="C111" s="20"/>
       <c r="D111" s="4">
         <v>500</v>
       </c>
@@ -11654,7 +11673,7 @@
       <c r="I111" s="6">
         <v>0</v>
       </c>
-      <c r="J111" s="10"/>
+      <c r="J111" s="20"/>
       <c r="K111" s="4">
         <v>500</v>
       </c>
@@ -11673,7 +11692,7 @@
       <c r="P111" s="6">
         <v>0</v>
       </c>
-      <c r="Q111" s="10"/>
+      <c r="Q111" s="20"/>
       <c r="R111" s="4">
         <v>500</v>
       </c>
@@ -11692,7 +11711,7 @@
       <c r="W111" s="6">
         <v>0</v>
       </c>
-      <c r="Y111" s="25"/>
+      <c r="Y111" s="15"/>
       <c r="Z111" s="4">
         <v>500</v>
       </c>
@@ -11716,7 +11735,7 @@
       <c r="B112" t="s">
         <v>28</v>
       </c>
-      <c r="C112" s="10"/>
+      <c r="C112" s="20"/>
       <c r="D112" s="4">
         <v>1000</v>
       </c>
@@ -11735,7 +11754,7 @@
       <c r="I112" s="6">
         <v>0</v>
       </c>
-      <c r="J112" s="10"/>
+      <c r="J112" s="20"/>
       <c r="K112" s="4">
         <v>1000</v>
       </c>
@@ -11754,7 +11773,7 @@
       <c r="P112" s="6">
         <v>0</v>
       </c>
-      <c r="Q112" s="10"/>
+      <c r="Q112" s="20"/>
       <c r="R112" s="4">
         <v>1000</v>
       </c>
@@ -11773,7 +11792,7 @@
       <c r="W112" s="6">
         <v>0</v>
       </c>
-      <c r="Y112" s="25"/>
+      <c r="Y112" s="15"/>
       <c r="Z112" s="4">
         <v>1000</v>
       </c>
@@ -11797,7 +11816,7 @@
       <c r="B113" t="s">
         <v>29</v>
       </c>
-      <c r="C113" s="9" t="s">
+      <c r="C113" s="21" t="s">
         <v>55</v>
       </c>
       <c r="D113" s="4">
@@ -11818,7 +11837,7 @@
       <c r="I113" s="6">
         <v>0</v>
       </c>
-      <c r="J113" s="9" t="s">
+      <c r="J113" s="21" t="s">
         <v>101</v>
       </c>
       <c r="K113" s="4">
@@ -11839,7 +11858,7 @@
       <c r="P113" s="6">
         <v>0</v>
       </c>
-      <c r="Q113" s="9" t="s">
+      <c r="Q113" s="21" t="s">
         <v>76</v>
       </c>
       <c r="R113" s="4">
@@ -11860,7 +11879,7 @@
       <c r="W113" s="6">
         <v>0</v>
       </c>
-      <c r="Y113" s="26" t="s">
+      <c r="Y113" s="14" t="s">
         <v>55</v>
       </c>
       <c r="Z113" s="4">
@@ -11886,7 +11905,7 @@
       <c r="B114" t="s">
         <v>29</v>
       </c>
-      <c r="C114" s="10"/>
+      <c r="C114" s="20"/>
       <c r="D114" s="4">
         <v>100</v>
       </c>
@@ -11905,7 +11924,7 @@
       <c r="I114" s="6">
         <v>0</v>
       </c>
-      <c r="J114" s="10"/>
+      <c r="J114" s="20"/>
       <c r="K114" s="4">
         <v>100</v>
       </c>
@@ -11924,7 +11943,7 @@
       <c r="P114" s="6">
         <v>0</v>
       </c>
-      <c r="Q114" s="10"/>
+      <c r="Q114" s="20"/>
       <c r="R114" s="4">
         <v>100</v>
       </c>
@@ -11943,7 +11962,7 @@
       <c r="W114" s="6">
         <v>0</v>
       </c>
-      <c r="Y114" s="25"/>
+      <c r="Y114" s="15"/>
       <c r="Z114" s="4">
         <v>100</v>
       </c>
@@ -11967,7 +11986,7 @@
       <c r="B115" t="s">
         <v>29</v>
       </c>
-      <c r="C115" s="10"/>
+      <c r="C115" s="20"/>
       <c r="D115" s="4">
         <v>200</v>
       </c>
@@ -11986,7 +12005,7 @@
       <c r="I115" s="6">
         <v>0</v>
       </c>
-      <c r="J115" s="10"/>
+      <c r="J115" s="20"/>
       <c r="K115" s="4">
         <v>200</v>
       </c>
@@ -12005,7 +12024,7 @@
       <c r="P115" s="6">
         <v>0</v>
       </c>
-      <c r="Q115" s="10"/>
+      <c r="Q115" s="20"/>
       <c r="R115" s="4">
         <v>200</v>
       </c>
@@ -12024,7 +12043,7 @@
       <c r="W115" s="6">
         <v>0</v>
       </c>
-      <c r="Y115" s="25"/>
+      <c r="Y115" s="15"/>
       <c r="Z115" s="4">
         <v>200</v>
       </c>
@@ -12048,7 +12067,7 @@
       <c r="B116" t="s">
         <v>29</v>
       </c>
-      <c r="C116" s="10"/>
+      <c r="C116" s="20"/>
       <c r="D116" s="4">
         <v>500</v>
       </c>
@@ -12067,7 +12086,7 @@
       <c r="I116" s="6">
         <v>0</v>
       </c>
-      <c r="J116" s="10"/>
+      <c r="J116" s="20"/>
       <c r="K116" s="4">
         <v>500</v>
       </c>
@@ -12086,7 +12105,7 @@
       <c r="P116" s="6">
         <v>0</v>
       </c>
-      <c r="Q116" s="10"/>
+      <c r="Q116" s="20"/>
       <c r="R116" s="4">
         <v>500</v>
       </c>
@@ -12105,7 +12124,7 @@
       <c r="W116" s="6">
         <v>0</v>
       </c>
-      <c r="Y116" s="25"/>
+      <c r="Y116" s="15"/>
       <c r="Z116" s="4">
         <v>500</v>
       </c>
@@ -12129,7 +12148,7 @@
       <c r="B117" t="s">
         <v>29</v>
       </c>
-      <c r="C117" s="10"/>
+      <c r="C117" s="20"/>
       <c r="D117" s="4">
         <v>1000</v>
       </c>
@@ -12148,7 +12167,7 @@
       <c r="I117" s="6">
         <v>0</v>
       </c>
-      <c r="J117" s="10"/>
+      <c r="J117" s="20"/>
       <c r="K117" s="4">
         <v>1000</v>
       </c>
@@ -12167,7 +12186,7 @@
       <c r="P117" s="6">
         <v>0</v>
       </c>
-      <c r="Q117" s="10"/>
+      <c r="Q117" s="20"/>
       <c r="R117" s="4">
         <v>1000</v>
       </c>
@@ -12186,7 +12205,7 @@
       <c r="W117" s="6">
         <v>0</v>
       </c>
-      <c r="Y117" s="25"/>
+      <c r="Y117" s="15"/>
       <c r="Z117" s="4">
         <v>1000</v>
       </c>
@@ -12210,7 +12229,7 @@
       <c r="B118" t="s">
         <v>30</v>
       </c>
-      <c r="C118" s="9" t="s">
+      <c r="C118" s="21" t="s">
         <v>56</v>
       </c>
       <c r="D118" s="4">
@@ -12231,7 +12250,7 @@
       <c r="I118" s="6">
         <v>0</v>
       </c>
-      <c r="J118" s="9" t="s">
+      <c r="J118" s="21" t="s">
         <v>102</v>
       </c>
       <c r="K118" s="4">
@@ -12252,7 +12271,7 @@
       <c r="P118" s="6">
         <v>0</v>
       </c>
-      <c r="Q118" s="9" t="s">
+      <c r="Q118" s="21" t="s">
         <v>77</v>
       </c>
       <c r="R118" s="4">
@@ -12273,7 +12292,7 @@
       <c r="W118" s="6">
         <v>0</v>
       </c>
-      <c r="Y118" s="26" t="s">
+      <c r="Y118" s="14" t="s">
         <v>56</v>
       </c>
       <c r="Z118" s="4">
@@ -12299,7 +12318,7 @@
       <c r="B119" t="s">
         <v>30</v>
       </c>
-      <c r="C119" s="10"/>
+      <c r="C119" s="20"/>
       <c r="D119" s="4">
         <v>100</v>
       </c>
@@ -12318,7 +12337,7 @@
       <c r="I119" s="6">
         <v>0</v>
       </c>
-      <c r="J119" s="10"/>
+      <c r="J119" s="20"/>
       <c r="K119" s="4">
         <v>100</v>
       </c>
@@ -12337,7 +12356,7 @@
       <c r="P119" s="6">
         <v>0</v>
       </c>
-      <c r="Q119" s="10"/>
+      <c r="Q119" s="20"/>
       <c r="R119" s="4">
         <v>100</v>
       </c>
@@ -12356,7 +12375,7 @@
       <c r="W119" s="6">
         <v>0</v>
       </c>
-      <c r="Y119" s="25"/>
+      <c r="Y119" s="15"/>
       <c r="Z119" s="4">
         <v>100</v>
       </c>
@@ -12380,7 +12399,7 @@
       <c r="B120" t="s">
         <v>30</v>
       </c>
-      <c r="C120" s="10"/>
+      <c r="C120" s="20"/>
       <c r="D120" s="4">
         <v>200</v>
       </c>
@@ -12399,7 +12418,7 @@
       <c r="I120" s="6">
         <v>0</v>
       </c>
-      <c r="J120" s="10"/>
+      <c r="J120" s="20"/>
       <c r="K120" s="4">
         <v>200</v>
       </c>
@@ -12418,7 +12437,7 @@
       <c r="P120" s="6">
         <v>0</v>
       </c>
-      <c r="Q120" s="10"/>
+      <c r="Q120" s="20"/>
       <c r="R120" s="4">
         <v>200</v>
       </c>
@@ -12437,7 +12456,7 @@
       <c r="W120" s="6">
         <v>0</v>
       </c>
-      <c r="Y120" s="25"/>
+      <c r="Y120" s="15"/>
       <c r="Z120" s="4">
         <v>200</v>
       </c>
@@ -12461,7 +12480,7 @@
       <c r="B121" t="s">
         <v>30</v>
       </c>
-      <c r="C121" s="10"/>
+      <c r="C121" s="20"/>
       <c r="D121" s="4">
         <v>500</v>
       </c>
@@ -12480,7 +12499,7 @@
       <c r="I121" s="6">
         <v>0</v>
       </c>
-      <c r="J121" s="10"/>
+      <c r="J121" s="20"/>
       <c r="K121" s="4">
         <v>500</v>
       </c>
@@ -12499,7 +12518,7 @@
       <c r="P121" s="6">
         <v>0</v>
       </c>
-      <c r="Q121" s="10"/>
+      <c r="Q121" s="20"/>
       <c r="R121" s="4">
         <v>500</v>
       </c>
@@ -12518,7 +12537,7 @@
       <c r="W121" s="6">
         <v>0</v>
       </c>
-      <c r="Y121" s="25"/>
+      <c r="Y121" s="15"/>
       <c r="Z121" s="4">
         <v>500</v>
       </c>
@@ -12542,7 +12561,7 @@
       <c r="B122" t="s">
         <v>30</v>
       </c>
-      <c r="C122" s="10"/>
+      <c r="C122" s="20"/>
       <c r="D122" s="4">
         <v>1000</v>
       </c>
@@ -12561,7 +12580,7 @@
       <c r="I122" s="6">
         <v>0</v>
       </c>
-      <c r="J122" s="10"/>
+      <c r="J122" s="20"/>
       <c r="K122" s="4">
         <v>1000</v>
       </c>
@@ -12580,7 +12599,7 @@
       <c r="P122" s="6">
         <v>0</v>
       </c>
-      <c r="Q122" s="10"/>
+      <c r="Q122" s="20"/>
       <c r="R122" s="4">
         <v>1000</v>
       </c>
@@ -12599,7 +12618,7 @@
       <c r="W122" s="6">
         <v>0</v>
       </c>
-      <c r="Y122" s="25"/>
+      <c r="Y122" s="15"/>
       <c r="Z122" s="4">
         <v>1000</v>
       </c>
@@ -12623,7 +12642,7 @@
       <c r="B123" t="s">
         <v>31</v>
       </c>
-      <c r="C123" s="9" t="s">
+      <c r="C123" s="21" t="s">
         <v>57</v>
       </c>
       <c r="D123" s="4">
@@ -12644,7 +12663,7 @@
       <c r="I123" s="6">
         <v>0</v>
       </c>
-      <c r="J123" s="9" t="s">
+      <c r="J123" s="21" t="s">
         <v>103</v>
       </c>
       <c r="K123" s="4">
@@ -12665,7 +12684,7 @@
       <c r="P123" s="6">
         <v>0</v>
       </c>
-      <c r="Q123" s="9" t="s">
+      <c r="Q123" s="21" t="s">
         <v>78</v>
       </c>
       <c r="R123" s="4">
@@ -12686,7 +12705,7 @@
       <c r="W123" s="6">
         <v>0</v>
       </c>
-      <c r="Y123" s="26" t="s">
+      <c r="Y123" s="14" t="s">
         <v>57</v>
       </c>
       <c r="Z123" s="4">
@@ -12712,7 +12731,7 @@
       <c r="B124" t="s">
         <v>31</v>
       </c>
-      <c r="C124" s="10"/>
+      <c r="C124" s="20"/>
       <c r="D124" s="4">
         <v>100</v>
       </c>
@@ -12731,7 +12750,7 @@
       <c r="I124" s="6">
         <v>0</v>
       </c>
-      <c r="J124" s="10"/>
+      <c r="J124" s="20"/>
       <c r="K124" s="4">
         <v>100</v>
       </c>
@@ -12750,7 +12769,7 @@
       <c r="P124" s="6">
         <v>0</v>
       </c>
-      <c r="Q124" s="10"/>
+      <c r="Q124" s="20"/>
       <c r="R124" s="4">
         <v>100</v>
       </c>
@@ -12769,7 +12788,7 @@
       <c r="W124" s="6">
         <v>0</v>
       </c>
-      <c r="Y124" s="25"/>
+      <c r="Y124" s="15"/>
       <c r="Z124" s="4">
         <v>100</v>
       </c>
@@ -12793,7 +12812,7 @@
       <c r="B125" t="s">
         <v>31</v>
       </c>
-      <c r="C125" s="10"/>
+      <c r="C125" s="20"/>
       <c r="D125" s="4">
         <v>200</v>
       </c>
@@ -12812,7 +12831,7 @@
       <c r="I125" s="6">
         <v>0</v>
       </c>
-      <c r="J125" s="10"/>
+      <c r="J125" s="20"/>
       <c r="K125" s="4">
         <v>200</v>
       </c>
@@ -12831,7 +12850,7 @@
       <c r="P125" s="6">
         <v>0</v>
       </c>
-      <c r="Q125" s="10"/>
+      <c r="Q125" s="20"/>
       <c r="R125" s="4">
         <v>200</v>
       </c>
@@ -12850,7 +12869,7 @@
       <c r="W125" s="6">
         <v>0</v>
       </c>
-      <c r="Y125" s="25"/>
+      <c r="Y125" s="15"/>
       <c r="Z125" s="4">
         <v>200</v>
       </c>
@@ -12874,7 +12893,7 @@
       <c r="B126" t="s">
         <v>31</v>
       </c>
-      <c r="C126" s="10"/>
+      <c r="C126" s="20"/>
       <c r="D126" s="4">
         <v>500</v>
       </c>
@@ -12893,7 +12912,7 @@
       <c r="I126" s="6">
         <v>0</v>
       </c>
-      <c r="J126" s="10"/>
+      <c r="J126" s="20"/>
       <c r="K126" s="4">
         <v>500</v>
       </c>
@@ -12912,7 +12931,7 @@
       <c r="P126" s="6">
         <v>0</v>
       </c>
-      <c r="Q126" s="10"/>
+      <c r="Q126" s="20"/>
       <c r="R126" s="4">
         <v>500</v>
       </c>
@@ -12931,7 +12950,7 @@
       <c r="W126" s="6">
         <v>0</v>
       </c>
-      <c r="Y126" s="25"/>
+      <c r="Y126" s="15"/>
       <c r="Z126" s="4">
         <v>500</v>
       </c>
@@ -12955,7 +12974,7 @@
       <c r="B127" t="s">
         <v>31</v>
       </c>
-      <c r="C127" s="10"/>
+      <c r="C127" s="20"/>
       <c r="D127" s="4">
         <v>1000</v>
       </c>
@@ -12974,7 +12993,7 @@
       <c r="I127" s="6">
         <v>0</v>
       </c>
-      <c r="J127" s="10"/>
+      <c r="J127" s="20"/>
       <c r="K127" s="4">
         <v>1000</v>
       </c>
@@ -12993,7 +13012,7 @@
       <c r="P127" s="6">
         <v>0</v>
       </c>
-      <c r="Q127" s="10"/>
+      <c r="Q127" s="20"/>
       <c r="R127" s="4">
         <v>1000</v>
       </c>
@@ -13012,7 +13031,7 @@
       <c r="W127" s="6">
         <v>0</v>
       </c>
-      <c r="Y127" s="25"/>
+      <c r="Y127" s="15"/>
       <c r="Z127" s="4">
         <v>1000</v>
       </c>
@@ -13036,7 +13055,7 @@
       <c r="B128" t="s">
         <v>32</v>
       </c>
-      <c r="C128" s="9" t="s">
+      <c r="C128" s="21" t="s">
         <v>58</v>
       </c>
       <c r="D128" s="4">
@@ -13057,7 +13076,7 @@
       <c r="I128" s="6">
         <v>0</v>
       </c>
-      <c r="J128" s="9" t="s">
+      <c r="J128" s="21" t="s">
         <v>104</v>
       </c>
       <c r="K128" s="4">
@@ -13076,7 +13095,7 @@
       <c r="P128" s="6">
         <v>0</v>
       </c>
-      <c r="Q128" s="9" t="s">
+      <c r="Q128" s="21" t="s">
         <v>79</v>
       </c>
       <c r="R128" s="4">
@@ -13097,7 +13116,7 @@
       <c r="W128" s="6">
         <v>0</v>
       </c>
-      <c r="Y128" s="26" t="s">
+      <c r="Y128" s="14" t="s">
         <v>58</v>
       </c>
       <c r="Z128" s="4">
@@ -13123,7 +13142,7 @@
       <c r="B129" t="s">
         <v>32</v>
       </c>
-      <c r="C129" s="10"/>
+      <c r="C129" s="20"/>
       <c r="D129" s="4">
         <v>100</v>
       </c>
@@ -13142,7 +13161,7 @@
       <c r="I129" s="6">
         <v>0</v>
       </c>
-      <c r="J129" s="10"/>
+      <c r="J129" s="20"/>
       <c r="K129" s="4">
         <v>100</v>
       </c>
@@ -13161,7 +13180,7 @@
       <c r="P129" s="6">
         <v>0</v>
       </c>
-      <c r="Q129" s="10"/>
+      <c r="Q129" s="20"/>
       <c r="R129" s="4">
         <v>100</v>
       </c>
@@ -13180,7 +13199,7 @@
       <c r="W129" s="6">
         <v>0</v>
       </c>
-      <c r="Y129" s="25"/>
+      <c r="Y129" s="15"/>
       <c r="Z129" s="4">
         <v>100</v>
       </c>
@@ -13204,7 +13223,7 @@
       <c r="B130" t="s">
         <v>32</v>
       </c>
-      <c r="C130" s="10"/>
+      <c r="C130" s="20"/>
       <c r="D130" s="4">
         <v>200</v>
       </c>
@@ -13223,7 +13242,7 @@
       <c r="I130" s="6">
         <v>0</v>
       </c>
-      <c r="J130" s="10"/>
+      <c r="J130" s="20"/>
       <c r="K130" s="4">
         <v>200</v>
       </c>
@@ -13242,7 +13261,7 @@
       <c r="P130" s="6">
         <v>0</v>
       </c>
-      <c r="Q130" s="10"/>
+      <c r="Q130" s="20"/>
       <c r="R130" s="4">
         <v>200</v>
       </c>
@@ -13261,7 +13280,7 @@
       <c r="W130" s="6">
         <v>0</v>
       </c>
-      <c r="Y130" s="25"/>
+      <c r="Y130" s="15"/>
       <c r="Z130" s="4">
         <v>200</v>
       </c>
@@ -13285,7 +13304,7 @@
       <c r="B131" t="s">
         <v>33</v>
       </c>
-      <c r="C131" s="9" t="s">
+      <c r="C131" s="21" t="s">
         <v>59</v>
       </c>
       <c r="D131" s="4">
@@ -13306,7 +13325,7 @@
       <c r="I131" s="6">
         <v>100</v>
       </c>
-      <c r="J131" s="9" t="s">
+      <c r="J131" s="21" t="s">
         <v>105</v>
       </c>
       <c r="K131" s="4">
@@ -13327,7 +13346,7 @@
       <c r="P131" s="6">
         <v>100</v>
       </c>
-      <c r="Q131" s="9" t="s">
+      <c r="Q131" s="21" t="s">
         <v>80</v>
       </c>
       <c r="R131" s="4">
@@ -13348,7 +13367,7 @@
       <c r="W131" s="6">
         <v>100</v>
       </c>
-      <c r="Y131" s="26" t="s">
+      <c r="Y131" s="14" t="s">
         <v>59</v>
       </c>
       <c r="Z131" s="4">
@@ -13374,7 +13393,7 @@
       <c r="B132" t="s">
         <v>33</v>
       </c>
-      <c r="C132" s="10"/>
+      <c r="C132" s="20"/>
       <c r="D132" s="4">
         <v>100</v>
       </c>
@@ -13393,7 +13412,7 @@
       <c r="I132" s="6">
         <v>200</v>
       </c>
-      <c r="J132" s="10"/>
+      <c r="J132" s="20"/>
       <c r="K132" s="4">
         <v>100</v>
       </c>
@@ -13412,7 +13431,7 @@
       <c r="P132" s="6">
         <v>200</v>
       </c>
-      <c r="Q132" s="10"/>
+      <c r="Q132" s="20"/>
       <c r="R132" s="4">
         <v>100</v>
       </c>
@@ -13431,7 +13450,7 @@
       <c r="W132" s="6">
         <v>200</v>
       </c>
-      <c r="Y132" s="25"/>
+      <c r="Y132" s="15"/>
       <c r="Z132" s="4">
         <v>100</v>
       </c>
@@ -13455,7 +13474,7 @@
       <c r="B133" t="s">
         <v>33</v>
       </c>
-      <c r="C133" s="10"/>
+      <c r="C133" s="20"/>
       <c r="D133" s="4">
         <v>200</v>
       </c>
@@ -13474,7 +13493,7 @@
       <c r="I133" s="6">
         <v>400</v>
       </c>
-      <c r="J133" s="10"/>
+      <c r="J133" s="20"/>
       <c r="K133" s="4">
         <v>200</v>
       </c>
@@ -13493,7 +13512,7 @@
       <c r="P133" s="6">
         <v>400</v>
       </c>
-      <c r="Q133" s="10"/>
+      <c r="Q133" s="20"/>
       <c r="R133" s="4">
         <v>200</v>
       </c>
@@ -13512,7 +13531,7 @@
       <c r="W133" s="6">
         <v>400</v>
       </c>
-      <c r="Y133" s="25"/>
+      <c r="Y133" s="15"/>
       <c r="Z133" s="4">
         <v>200</v>
       </c>
@@ -13536,7 +13555,7 @@
       <c r="B134" t="s">
         <v>34</v>
       </c>
-      <c r="C134" s="9" t="s">
+      <c r="C134" s="21" t="s">
         <v>60</v>
       </c>
       <c r="D134" s="4">
@@ -13557,7 +13576,7 @@
       <c r="I134" s="6">
         <v>0</v>
       </c>
-      <c r="J134" s="9" t="s">
+      <c r="J134" s="21" t="s">
         <v>81</v>
       </c>
       <c r="K134" s="4">
@@ -13578,28 +13597,28 @@
       <c r="P134" s="6">
         <v>0</v>
       </c>
-      <c r="Q134" s="9" t="s">
+      <c r="Q134" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="R134" s="4">
+      <c r="R134" s="11">
         <v>50</v>
       </c>
-      <c r="S134" s="4">
+      <c r="S134" s="11">
         <v>24100</v>
       </c>
-      <c r="T134" s="4">
+      <c r="T134" s="11">
         <v>2.0699999999999998</v>
       </c>
-      <c r="U134" s="4">
+      <c r="U134" s="11">
         <v>22.63</v>
       </c>
-      <c r="V134" s="4">
+      <c r="V134" s="11">
         <v>361504</v>
       </c>
-      <c r="W134" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y134" s="26" t="s">
+      <c r="W134" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y134" s="14" t="s">
         <v>60</v>
       </c>
       <c r="Z134" s="4">
@@ -13625,7 +13644,7 @@
       <c r="B135" t="s">
         <v>34</v>
       </c>
-      <c r="C135" s="10"/>
+      <c r="C135" s="20"/>
       <c r="D135" s="4">
         <v>100</v>
       </c>
@@ -13644,7 +13663,7 @@
       <c r="I135" s="6">
         <v>0</v>
       </c>
-      <c r="J135" s="10"/>
+      <c r="J135" s="20"/>
       <c r="K135" s="4">
         <v>100</v>
       </c>
@@ -13663,26 +13682,26 @@
       <c r="P135" s="6">
         <v>0</v>
       </c>
-      <c r="Q135" s="10"/>
-      <c r="R135" s="4">
+      <c r="Q135" s="25"/>
+      <c r="R135" s="11">
         <v>100</v>
       </c>
-      <c r="S135" s="4">
+      <c r="S135" s="11">
         <v>23862</v>
       </c>
-      <c r="T135" s="4">
+      <c r="T135" s="11">
         <v>4.1900000000000004</v>
       </c>
-      <c r="U135" s="4">
+      <c r="U135" s="11">
         <v>40.81</v>
       </c>
-      <c r="V135" s="4">
+      <c r="V135" s="11">
         <v>357429</v>
       </c>
-      <c r="W135" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y135" s="25"/>
+      <c r="W135" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y135" s="15"/>
       <c r="Z135" s="4">
         <v>100</v>
       </c>
@@ -13706,7 +13725,7 @@
       <c r="B136" t="s">
         <v>34</v>
       </c>
-      <c r="C136" s="10"/>
+      <c r="C136" s="20"/>
       <c r="D136" s="4">
         <v>200</v>
       </c>
@@ -13725,7 +13744,7 @@
       <c r="I136" s="6">
         <v>0</v>
       </c>
-      <c r="J136" s="10"/>
+      <c r="J136" s="20"/>
       <c r="K136" s="4">
         <v>200</v>
       </c>
@@ -13744,26 +13763,26 @@
       <c r="P136" s="6">
         <v>0</v>
       </c>
-      <c r="Q136" s="10"/>
-      <c r="R136" s="4">
+      <c r="Q136" s="25"/>
+      <c r="R136" s="11">
         <v>200</v>
       </c>
-      <c r="S136" s="4">
+      <c r="S136" s="11">
         <v>24060</v>
       </c>
-      <c r="T136" s="4">
+      <c r="T136" s="11">
         <v>8.31</v>
       </c>
-      <c r="U136" s="4">
+      <c r="U136" s="11">
         <v>56.42</v>
       </c>
-      <c r="V136" s="4">
+      <c r="V136" s="11">
         <v>360050</v>
       </c>
-      <c r="W136" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y136" s="25"/>
+      <c r="W136" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="15"/>
       <c r="Z136" s="4">
         <v>200</v>
       </c>
@@ -13787,7 +13806,7 @@
       <c r="B137" t="s">
         <v>34</v>
       </c>
-      <c r="C137" s="10"/>
+      <c r="C137" s="20"/>
       <c r="D137" s="4">
         <v>500</v>
       </c>
@@ -13806,7 +13825,7 @@
       <c r="I137" s="6">
         <v>0</v>
       </c>
-      <c r="J137" s="10"/>
+      <c r="J137" s="20"/>
       <c r="K137" s="4">
         <v>500</v>
       </c>
@@ -13825,26 +13844,26 @@
       <c r="P137" s="6">
         <v>0</v>
       </c>
-      <c r="Q137" s="10"/>
-      <c r="R137" s="4">
+      <c r="Q137" s="25"/>
+      <c r="R137" s="11">
         <v>500</v>
       </c>
-      <c r="S137" s="4">
+      <c r="S137" s="11">
         <v>23305</v>
       </c>
-      <c r="T137" s="4">
+      <c r="T137" s="11">
         <v>21.45</v>
       </c>
-      <c r="U137" s="4">
+      <c r="U137" s="11">
         <v>127.27</v>
       </c>
-      <c r="V137" s="4">
+      <c r="V137" s="11">
         <v>347963</v>
       </c>
-      <c r="W137" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y137" s="25"/>
+      <c r="W137" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y137" s="15"/>
       <c r="Z137" s="4">
         <v>500</v>
       </c>
@@ -13868,7 +13887,7 @@
       <c r="B138" t="s">
         <v>34</v>
       </c>
-      <c r="C138" s="10"/>
+      <c r="C138" s="20"/>
       <c r="D138" s="4">
         <v>1000</v>
       </c>
@@ -13887,7 +13906,7 @@
       <c r="I138" s="6">
         <v>0</v>
       </c>
-      <c r="J138" s="10"/>
+      <c r="J138" s="20"/>
       <c r="K138" s="4">
         <v>1000</v>
       </c>
@@ -13906,26 +13925,26 @@
       <c r="P138" s="6">
         <v>0</v>
       </c>
-      <c r="Q138" s="10"/>
-      <c r="R138" s="4">
+      <c r="Q138" s="25"/>
+      <c r="R138" s="11">
         <v>1000</v>
       </c>
-      <c r="S138" s="4">
+      <c r="S138" s="11">
         <v>22548</v>
       </c>
-      <c r="T138" s="4">
+      <c r="T138" s="11">
         <v>44.34</v>
       </c>
-      <c r="U138" s="4">
+      <c r="U138" s="11">
         <v>187.59</v>
       </c>
-      <c r="V138" s="4">
+      <c r="V138" s="11">
         <v>336471</v>
       </c>
-      <c r="W138" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y138" s="25"/>
+      <c r="W138" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y138" s="15"/>
       <c r="Z138" s="4">
         <v>1000</v>
       </c>
@@ -13949,7 +13968,7 @@
       <c r="B139" t="s">
         <v>35</v>
       </c>
-      <c r="C139" s="9" t="s">
+      <c r="C139" s="21" t="s">
         <v>61</v>
       </c>
       <c r="D139" s="4">
@@ -13970,7 +13989,7 @@
       <c r="I139" s="6">
         <v>0</v>
       </c>
-      <c r="J139" s="9" t="s">
+      <c r="J139" s="21" t="s">
         <v>106</v>
       </c>
       <c r="K139" s="4">
@@ -13991,28 +14010,28 @@
       <c r="P139" s="6">
         <v>0</v>
       </c>
-      <c r="Q139" s="9" t="s">
+      <c r="Q139" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="R139" s="4">
+      <c r="R139" s="11">
         <v>50</v>
       </c>
-      <c r="S139" s="4">
+      <c r="S139" s="11">
         <v>2981</v>
       </c>
-      <c r="T139" s="4">
+      <c r="T139" s="11">
         <v>16.77</v>
       </c>
-      <c r="U139" s="4">
+      <c r="U139" s="11">
         <v>96.63</v>
       </c>
-      <c r="V139" s="4">
+      <c r="V139" s="11">
         <v>44746</v>
       </c>
-      <c r="W139" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y139" s="26" t="s">
+      <c r="W139" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y139" s="14" t="s">
         <v>61</v>
       </c>
       <c r="Z139" s="4">
@@ -14038,7 +14057,7 @@
       <c r="B140" t="s">
         <v>35</v>
       </c>
-      <c r="C140" s="10"/>
+      <c r="C140" s="20"/>
       <c r="D140" s="4">
         <v>100</v>
       </c>
@@ -14057,7 +14076,7 @@
       <c r="I140" s="6">
         <v>0</v>
       </c>
-      <c r="J140" s="10"/>
+      <c r="J140" s="20"/>
       <c r="K140" s="4">
         <v>100</v>
       </c>
@@ -14076,26 +14095,26 @@
       <c r="P140" s="6">
         <v>0</v>
       </c>
-      <c r="Q140" s="10"/>
-      <c r="R140" s="4">
+      <c r="Q140" s="25"/>
+      <c r="R140" s="11">
         <v>100</v>
       </c>
-      <c r="S140" s="4">
+      <c r="S140" s="11">
         <v>2984</v>
       </c>
-      <c r="T140" s="4">
+      <c r="T140" s="11">
         <v>33.54</v>
       </c>
-      <c r="U140" s="4">
+      <c r="U140" s="11">
         <v>105.29</v>
       </c>
-      <c r="V140" s="4">
+      <c r="V140" s="11">
         <v>44690</v>
       </c>
-      <c r="W140" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y140" s="25"/>
+      <c r="W140" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y140" s="15"/>
       <c r="Z140" s="4">
         <v>100</v>
       </c>
@@ -14119,7 +14138,7 @@
       <c r="B141" t="s">
         <v>35</v>
       </c>
-      <c r="C141" s="10"/>
+      <c r="C141" s="20"/>
       <c r="D141" s="4">
         <v>200</v>
       </c>
@@ -14138,7 +14157,7 @@
       <c r="I141" s="6">
         <v>0</v>
       </c>
-      <c r="J141" s="10"/>
+      <c r="J141" s="20"/>
       <c r="K141" s="4">
         <v>200</v>
       </c>
@@ -14157,26 +14176,26 @@
       <c r="P141" s="6">
         <v>0</v>
       </c>
-      <c r="Q141" s="10"/>
-      <c r="R141" s="4">
+      <c r="Q141" s="25"/>
+      <c r="R141" s="11">
         <v>200</v>
       </c>
-      <c r="S141" s="4">
+      <c r="S141" s="11">
         <v>3688</v>
       </c>
-      <c r="T141" s="4">
+      <c r="T141" s="11">
         <v>54.09</v>
       </c>
-      <c r="U141" s="4">
+      <c r="U141" s="11">
         <v>141.97</v>
       </c>
-      <c r="V141" s="4">
+      <c r="V141" s="11">
         <v>10620</v>
       </c>
-      <c r="W141" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y141" s="25"/>
+      <c r="W141" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="15"/>
       <c r="Z141" s="4">
         <v>200</v>
       </c>
@@ -14200,7 +14219,7 @@
       <c r="B142" t="s">
         <v>35</v>
       </c>
-      <c r="C142" s="10"/>
+      <c r="C142" s="20"/>
       <c r="D142" s="4">
         <v>500</v>
       </c>
@@ -14219,7 +14238,7 @@
       <c r="I142" s="6">
         <v>0</v>
       </c>
-      <c r="J142" s="10"/>
+      <c r="J142" s="20"/>
       <c r="K142" s="4">
         <v>500</v>
       </c>
@@ -14238,26 +14257,26 @@
       <c r="P142" s="6">
         <v>0</v>
       </c>
-      <c r="Q142" s="10"/>
-      <c r="R142" s="4">
+      <c r="Q142" s="25"/>
+      <c r="R142" s="11">
         <v>500</v>
       </c>
-      <c r="S142" s="4">
+      <c r="S142" s="11">
         <v>3260</v>
       </c>
-      <c r="T142" s="4">
+      <c r="T142" s="11">
         <v>151.91</v>
       </c>
-      <c r="U142" s="4">
+      <c r="U142" s="11">
         <v>375.33</v>
       </c>
-      <c r="V142" s="4">
+      <c r="V142" s="11">
         <v>30908</v>
       </c>
-      <c r="W142" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y142" s="25"/>
+      <c r="W142" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y142" s="15"/>
       <c r="Z142" s="4">
         <v>500</v>
       </c>
@@ -14281,7 +14300,7 @@
       <c r="B143" t="s">
         <v>35</v>
       </c>
-      <c r="C143" s="10"/>
+      <c r="C143" s="20"/>
       <c r="D143" s="4">
         <v>1000</v>
       </c>
@@ -14300,7 +14319,7 @@
       <c r="I143" s="6">
         <v>0</v>
       </c>
-      <c r="J143" s="10"/>
+      <c r="J143" s="20"/>
       <c r="K143" s="4">
         <v>1000</v>
       </c>
@@ -14319,26 +14338,26 @@
       <c r="P143" s="6">
         <v>0</v>
       </c>
-      <c r="Q143" s="10"/>
-      <c r="R143" s="4">
+      <c r="Q143" s="25"/>
+      <c r="R143" s="11">
         <v>1000</v>
       </c>
-      <c r="S143" s="4">
+      <c r="S143" s="11">
         <v>3082</v>
       </c>
-      <c r="T143" s="4">
+      <c r="T143" s="11">
         <v>324.33999999999997</v>
       </c>
-      <c r="U143" s="4">
+      <c r="U143" s="11">
         <v>741.99</v>
       </c>
-      <c r="V143" s="4">
+      <c r="V143" s="11">
         <v>46762</v>
       </c>
-      <c r="W143" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y143" s="25"/>
+      <c r="W143" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y143" s="15"/>
       <c r="Z143" s="4">
         <v>1000</v>
       </c>
@@ -14362,7 +14381,7 @@
       <c r="B144" t="s">
         <v>36</v>
       </c>
-      <c r="C144" s="9" t="s">
+      <c r="C144" s="21" t="s">
         <v>62</v>
       </c>
       <c r="D144" s="4">
@@ -14383,7 +14402,7 @@
       <c r="I144" s="6">
         <v>0</v>
       </c>
-      <c r="J144" s="9" t="s">
+      <c r="J144" s="21" t="s">
         <v>62</v>
       </c>
       <c r="K144" s="4">
@@ -14404,28 +14423,28 @@
       <c r="P144" s="6">
         <v>0</v>
       </c>
-      <c r="Q144" s="9" t="s">
+      <c r="Q144" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="R144" s="4">
+      <c r="R144" s="11">
         <v>50</v>
       </c>
-      <c r="S144" s="4">
+      <c r="S144" s="11">
         <v>486</v>
       </c>
-      <c r="T144" s="4">
+      <c r="T144" s="11">
         <v>102.48</v>
       </c>
-      <c r="U144" s="4">
+      <c r="U144" s="11">
         <v>132.75</v>
       </c>
-      <c r="V144" s="4">
+      <c r="V144" s="11">
         <v>7350</v>
       </c>
-      <c r="W144" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y144" s="26" t="s">
+      <c r="W144" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y144" s="14" t="s">
         <v>62</v>
       </c>
       <c r="Z144" s="4">
@@ -14451,7 +14470,7 @@
       <c r="B145" t="s">
         <v>36</v>
       </c>
-      <c r="C145" s="10"/>
+      <c r="C145" s="20"/>
       <c r="D145" s="4">
         <v>100</v>
       </c>
@@ -14470,7 +14489,7 @@
       <c r="I145" s="6">
         <v>0</v>
       </c>
-      <c r="J145" s="10"/>
+      <c r="J145" s="20"/>
       <c r="K145" s="4">
         <v>100</v>
       </c>
@@ -14489,26 +14508,26 @@
       <c r="P145" s="6">
         <v>0</v>
       </c>
-      <c r="Q145" s="10"/>
-      <c r="R145" s="4">
+      <c r="Q145" s="25"/>
+      <c r="R145" s="11">
         <v>100</v>
       </c>
-      <c r="S145" s="4">
+      <c r="S145" s="11">
         <v>974</v>
       </c>
-      <c r="T145" s="4">
+      <c r="T145" s="11">
         <v>102.45</v>
       </c>
-      <c r="U145" s="4">
+      <c r="U145" s="11">
         <v>143.44999999999999</v>
       </c>
-      <c r="V145" s="4">
+      <c r="V145" s="11">
         <v>14672</v>
       </c>
-      <c r="W145" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y145" s="25"/>
+      <c r="W145" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y145" s="15"/>
       <c r="Z145" s="4">
         <v>100</v>
       </c>
@@ -14532,7 +14551,7 @@
       <c r="B146" t="s">
         <v>36</v>
       </c>
-      <c r="C146" s="10"/>
+      <c r="C146" s="20"/>
       <c r="D146" s="4">
         <v>200</v>
       </c>
@@ -14551,7 +14570,7 @@
       <c r="I146" s="6">
         <v>0</v>
       </c>
-      <c r="J146" s="10"/>
+      <c r="J146" s="20"/>
       <c r="K146" s="4">
         <v>200</v>
       </c>
@@ -14570,26 +14589,26 @@
       <c r="P146" s="6">
         <v>0</v>
       </c>
-      <c r="Q146" s="10"/>
-      <c r="R146" s="4">
+      <c r="Q146" s="25"/>
+      <c r="R146" s="11">
         <v>200</v>
       </c>
-      <c r="S146" s="4">
+      <c r="S146" s="11">
         <v>2310</v>
       </c>
-      <c r="T146" s="4">
+      <c r="T146" s="11">
         <v>86.53</v>
       </c>
-      <c r="U146" s="4">
+      <c r="U146" s="11">
         <v>803.2</v>
       </c>
-      <c r="V146" s="4">
+      <c r="V146" s="11">
         <v>20671</v>
       </c>
-      <c r="W146" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y146" s="25"/>
+      <c r="W146" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y146" s="15"/>
       <c r="Z146" s="4">
         <v>200</v>
       </c>
@@ -14613,7 +14632,7 @@
       <c r="B147" t="s">
         <v>36</v>
       </c>
-      <c r="C147" s="10"/>
+      <c r="C147" s="20"/>
       <c r="D147" s="4">
         <v>500</v>
       </c>
@@ -14632,7 +14651,7 @@
       <c r="I147" s="6">
         <v>0</v>
       </c>
-      <c r="J147" s="10"/>
+      <c r="J147" s="20"/>
       <c r="K147" s="4">
         <v>500</v>
       </c>
@@ -14651,26 +14670,26 @@
       <c r="P147" s="6">
         <v>0</v>
       </c>
-      <c r="Q147" s="10"/>
-      <c r="R147" s="4">
+      <c r="Q147" s="25"/>
+      <c r="R147" s="11">
         <v>500</v>
       </c>
-      <c r="S147" s="4">
+      <c r="S147" s="11">
         <v>2623</v>
       </c>
-      <c r="T147" s="4">
+      <c r="T147" s="11">
         <v>189.97</v>
       </c>
-      <c r="U147" s="4">
+      <c r="U147" s="11">
         <v>388.78</v>
       </c>
-      <c r="V147" s="4">
+      <c r="V147" s="11">
         <v>39644</v>
       </c>
-      <c r="W147" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y147" s="25"/>
+      <c r="W147" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y147" s="15"/>
       <c r="Z147" s="4">
         <v>500</v>
       </c>
@@ -14694,7 +14713,7 @@
       <c r="B148" t="s">
         <v>36</v>
       </c>
-      <c r="C148" s="10"/>
+      <c r="C148" s="20"/>
       <c r="D148" s="4">
         <v>1000</v>
       </c>
@@ -14713,7 +14732,7 @@
       <c r="I148" s="6">
         <v>0</v>
       </c>
-      <c r="J148" s="10"/>
+      <c r="J148" s="20"/>
       <c r="K148" s="4">
         <v>1000</v>
       </c>
@@ -14732,26 +14751,26 @@
       <c r="P148" s="6">
         <v>0</v>
       </c>
-      <c r="Q148" s="10"/>
-      <c r="R148" s="4">
+      <c r="Q148" s="25"/>
+      <c r="R148" s="11">
         <v>1000</v>
       </c>
-      <c r="S148" s="4">
+      <c r="S148" s="11">
         <v>2703</v>
       </c>
-      <c r="T148" s="4">
+      <c r="T148" s="11">
         <v>364.15</v>
       </c>
-      <c r="U148" s="4">
+      <c r="U148" s="11">
         <v>809.34</v>
       </c>
-      <c r="V148" s="4">
+      <c r="V148" s="11">
         <v>40188</v>
       </c>
-      <c r="W148" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y148" s="25"/>
+      <c r="W148" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y148" s="15"/>
       <c r="Z148" s="4">
         <v>1000</v>
       </c>
@@ -14775,7 +14794,7 @@
       <c r="B149" t="s">
         <v>37</v>
       </c>
-      <c r="C149" s="9" t="s">
+      <c r="C149" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D149" s="4">
@@ -14796,7 +14815,7 @@
       <c r="I149" s="6">
         <v>0</v>
       </c>
-      <c r="J149" s="9" t="s">
+      <c r="J149" s="21" t="s">
         <v>107</v>
       </c>
       <c r="K149" s="4">
@@ -14817,28 +14836,28 @@
       <c r="P149" s="6">
         <v>0</v>
       </c>
-      <c r="Q149" s="9" t="s">
+      <c r="Q149" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="R149" s="4">
+      <c r="R149" s="11">
         <v>50</v>
       </c>
-      <c r="S149" s="4">
+      <c r="S149" s="11">
         <v>3855</v>
       </c>
-      <c r="T149" s="4">
+      <c r="T149" s="11">
         <v>12.97</v>
       </c>
-      <c r="U149" s="4">
+      <c r="U149" s="11">
         <v>50.85</v>
       </c>
-      <c r="V149" s="4">
-        <v>0</v>
-      </c>
-      <c r="W149" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y149" s="26" t="s">
+      <c r="V149" s="11">
+        <v>0</v>
+      </c>
+      <c r="W149" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y149" s="14" t="s">
         <v>63</v>
       </c>
       <c r="Z149" s="4">
@@ -14864,7 +14883,7 @@
       <c r="B150" t="s">
         <v>37</v>
       </c>
-      <c r="C150" s="10"/>
+      <c r="C150" s="20"/>
       <c r="D150" s="4">
         <v>100</v>
       </c>
@@ -14883,7 +14902,7 @@
       <c r="I150" s="6">
         <v>0</v>
       </c>
-      <c r="J150" s="10"/>
+      <c r="J150" s="20"/>
       <c r="K150" s="4">
         <v>100</v>
       </c>
@@ -14902,26 +14921,26 @@
       <c r="P150" s="6">
         <v>0</v>
       </c>
-      <c r="Q150" s="10"/>
-      <c r="R150" s="4">
+      <c r="Q150" s="25"/>
+      <c r="R150" s="11">
         <v>100</v>
       </c>
-      <c r="S150" s="4">
+      <c r="S150" s="11">
         <v>2173</v>
       </c>
-      <c r="T150" s="4">
+      <c r="T150" s="11">
         <v>45.92</v>
       </c>
-      <c r="U150" s="4">
+      <c r="U150" s="11">
         <v>218.5</v>
       </c>
-      <c r="V150" s="4">
+      <c r="V150" s="11">
         <v>22157</v>
       </c>
-      <c r="W150" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y150" s="25"/>
+      <c r="W150" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y150" s="15"/>
       <c r="Z150" s="4">
         <v>100</v>
       </c>
@@ -14945,7 +14964,7 @@
       <c r="B151" t="s">
         <v>37</v>
       </c>
-      <c r="C151" s="10"/>
+      <c r="C151" s="20"/>
       <c r="D151" s="4">
         <v>200</v>
       </c>
@@ -14964,7 +14983,7 @@
       <c r="I151" s="6">
         <v>0</v>
       </c>
-      <c r="J151" s="10"/>
+      <c r="J151" s="20"/>
       <c r="K151" s="4">
         <v>200</v>
       </c>
@@ -14983,26 +15002,26 @@
       <c r="P151" s="6">
         <v>0</v>
       </c>
-      <c r="Q151" s="10"/>
-      <c r="R151" s="4">
+      <c r="Q151" s="25"/>
+      <c r="R151" s="11">
         <v>200</v>
       </c>
-      <c r="S151" s="4">
+      <c r="S151" s="11">
         <v>2553</v>
       </c>
-      <c r="T151" s="4">
+      <c r="T151" s="11">
         <v>78.23</v>
       </c>
-      <c r="U151" s="4">
+      <c r="U151" s="11">
         <v>237.82</v>
       </c>
-      <c r="V151" s="4">
+      <c r="V151" s="11">
         <v>38352</v>
       </c>
-      <c r="W151" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y151" s="25"/>
+      <c r="W151" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="15"/>
       <c r="Z151" s="4">
         <v>200</v>
       </c>
@@ -15026,7 +15045,7 @@
       <c r="B152" t="s">
         <v>37</v>
       </c>
-      <c r="C152" s="10"/>
+      <c r="C152" s="20"/>
       <c r="D152" s="4">
         <v>500</v>
       </c>
@@ -15045,7 +15064,7 @@
       <c r="I152" s="6">
         <v>0</v>
       </c>
-      <c r="J152" s="10"/>
+      <c r="J152" s="20"/>
       <c r="K152" s="4">
         <v>500</v>
       </c>
@@ -15064,26 +15083,26 @@
       <c r="P152" s="6">
         <v>0</v>
       </c>
-      <c r="Q152" s="10"/>
-      <c r="R152" s="4">
+      <c r="Q152" s="25"/>
+      <c r="R152" s="11">
         <v>500</v>
       </c>
-      <c r="S152" s="4">
+      <c r="S152" s="11">
         <v>2755</v>
       </c>
-      <c r="T152" s="4">
+      <c r="T152" s="11">
         <v>180.15</v>
       </c>
-      <c r="U152" s="4">
+      <c r="U152" s="11">
         <v>473.51</v>
       </c>
-      <c r="V152" s="4">
+      <c r="V152" s="11">
         <v>39639</v>
       </c>
-      <c r="W152" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y152" s="25"/>
+      <c r="W152" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y152" s="15"/>
       <c r="Z152" s="4">
         <v>500</v>
       </c>
@@ -15107,7 +15126,7 @@
       <c r="B153" t="s">
         <v>37</v>
       </c>
-      <c r="C153" s="10"/>
+      <c r="C153" s="20"/>
       <c r="D153" s="4">
         <v>1000</v>
       </c>
@@ -15126,7 +15145,7 @@
       <c r="I153" s="6">
         <v>0</v>
       </c>
-      <c r="J153" s="10"/>
+      <c r="J153" s="20"/>
       <c r="K153" s="4">
         <v>1000</v>
       </c>
@@ -15145,26 +15164,26 @@
       <c r="P153" s="6">
         <v>0</v>
       </c>
-      <c r="Q153" s="10"/>
-      <c r="R153" s="4">
+      <c r="Q153" s="25"/>
+      <c r="R153" s="11">
         <v>1000</v>
       </c>
-      <c r="S153" s="4">
+      <c r="S153" s="11">
         <v>3830</v>
       </c>
-      <c r="T153" s="4">
+      <c r="T153" s="11">
         <v>259.32</v>
       </c>
-      <c r="U153" s="4">
+      <c r="U153" s="11">
         <v>565.57000000000005</v>
       </c>
-      <c r="V153" s="4">
-        <v>0</v>
-      </c>
-      <c r="W153" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y153" s="25"/>
+      <c r="V153" s="11">
+        <v>0</v>
+      </c>
+      <c r="W153" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y153" s="15"/>
       <c r="Z153" s="4">
         <v>1000</v>
       </c>
@@ -15188,7 +15207,7 @@
       <c r="B154" t="s">
         <v>38</v>
       </c>
-      <c r="C154" s="9" t="s">
+      <c r="C154" s="21" t="s">
         <v>64</v>
       </c>
       <c r="D154" s="4">
@@ -15209,7 +15228,7 @@
       <c r="I154" s="6">
         <v>0</v>
       </c>
-      <c r="J154" s="9" t="s">
+      <c r="J154" s="21" t="s">
         <v>108</v>
       </c>
       <c r="K154" s="4">
@@ -15230,28 +15249,28 @@
       <c r="P154" s="6">
         <v>0</v>
       </c>
-      <c r="Q154" s="9" t="s">
+      <c r="Q154" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="R154" s="4">
+      <c r="R154" s="11">
         <v>50</v>
       </c>
-      <c r="S154" s="4">
+      <c r="S154" s="11">
         <v>487</v>
       </c>
-      <c r="T154" s="4">
+      <c r="T154" s="11">
         <v>58.34</v>
       </c>
-      <c r="U154" s="4">
+      <c r="U154" s="11">
         <v>144.26</v>
       </c>
-      <c r="V154" s="4">
+      <c r="V154" s="11">
         <v>6550</v>
       </c>
-      <c r="W154" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y154" s="26" t="s">
+      <c r="W154" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y154" s="14" t="s">
         <v>64</v>
       </c>
       <c r="Z154" s="4">
@@ -15277,7 +15296,7 @@
       <c r="B155" t="s">
         <v>38</v>
       </c>
-      <c r="C155" s="10"/>
+      <c r="C155" s="20"/>
       <c r="D155" s="4">
         <v>100</v>
       </c>
@@ -15296,7 +15315,7 @@
       <c r="I155" s="6">
         <v>0</v>
       </c>
-      <c r="J155" s="10"/>
+      <c r="J155" s="20"/>
       <c r="K155" s="4">
         <v>100</v>
       </c>
@@ -15315,26 +15334,26 @@
       <c r="P155" s="6">
         <v>0</v>
       </c>
-      <c r="Q155" s="10"/>
-      <c r="R155" s="4">
+      <c r="Q155" s="25"/>
+      <c r="R155" s="11">
         <v>100</v>
       </c>
-      <c r="S155" s="4">
+      <c r="S155" s="11">
         <v>974</v>
       </c>
-      <c r="T155" s="4">
+      <c r="T155" s="11">
         <v>102.51</v>
       </c>
-      <c r="U155" s="4">
+      <c r="U155" s="11">
         <v>156.72</v>
       </c>
-      <c r="V155" s="4">
+      <c r="V155" s="11">
         <v>14668</v>
       </c>
-      <c r="W155" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y155" s="25"/>
+      <c r="W155" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y155" s="15"/>
       <c r="Z155" s="4">
         <v>100</v>
       </c>
@@ -15358,7 +15377,7 @@
       <c r="B156" t="s">
         <v>38</v>
       </c>
-      <c r="C156" s="10"/>
+      <c r="C156" s="20"/>
       <c r="D156" s="4">
         <v>200</v>
       </c>
@@ -15377,7 +15396,7 @@
       <c r="I156" s="6">
         <v>0</v>
       </c>
-      <c r="J156" s="10"/>
+      <c r="J156" s="20"/>
       <c r="K156" s="4">
         <v>200</v>
       </c>
@@ -15396,26 +15415,26 @@
       <c r="P156" s="6">
         <v>0</v>
       </c>
-      <c r="Q156" s="10"/>
-      <c r="R156" s="4">
+      <c r="Q156" s="25"/>
+      <c r="R156" s="11">
         <v>200</v>
       </c>
-      <c r="S156" s="4">
+      <c r="S156" s="11">
         <v>1864</v>
       </c>
-      <c r="T156" s="4">
+      <c r="T156" s="11">
         <v>107.07</v>
       </c>
-      <c r="U156" s="4">
+      <c r="U156" s="11">
         <v>156.11000000000001</v>
       </c>
-      <c r="V156" s="4">
+      <c r="V156" s="11">
         <v>28073</v>
       </c>
-      <c r="W156" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y156" s="25"/>
+      <c r="W156" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y156" s="15"/>
       <c r="Z156" s="4">
         <v>200</v>
       </c>
@@ -15439,7 +15458,7 @@
       <c r="B157" t="s">
         <v>38</v>
       </c>
-      <c r="C157" s="10"/>
+      <c r="C157" s="20"/>
       <c r="D157" s="4">
         <v>500</v>
       </c>
@@ -15458,7 +15477,7 @@
       <c r="I157" s="6">
         <v>0</v>
       </c>
-      <c r="J157" s="10"/>
+      <c r="J157" s="20"/>
       <c r="K157" s="4">
         <v>500</v>
       </c>
@@ -15477,26 +15496,26 @@
       <c r="P157" s="6">
         <v>0</v>
       </c>
-      <c r="Q157" s="10"/>
-      <c r="R157" s="4">
+      <c r="Q157" s="25"/>
+      <c r="R157" s="11">
         <v>500</v>
       </c>
-      <c r="S157" s="4">
+      <c r="S157" s="11">
         <v>2644</v>
       </c>
-      <c r="T157" s="4">
+      <c r="T157" s="11">
         <v>187.9</v>
       </c>
-      <c r="U157" s="4">
+      <c r="U157" s="11">
         <v>401.09</v>
       </c>
-      <c r="V157" s="4">
+      <c r="V157" s="11">
         <v>39917</v>
       </c>
-      <c r="W157" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y157" s="25"/>
+      <c r="W157" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="15"/>
       <c r="Z157" s="4">
         <v>500</v>
       </c>
@@ -15520,7 +15539,7 @@
       <c r="B158" t="s">
         <v>38</v>
       </c>
-      <c r="C158" s="10"/>
+      <c r="C158" s="20"/>
       <c r="D158" s="4">
         <v>1000</v>
       </c>
@@ -15539,7 +15558,7 @@
       <c r="I158" s="6">
         <v>0</v>
       </c>
-      <c r="J158" s="10"/>
+      <c r="J158" s="20"/>
       <c r="K158" s="4">
         <v>1000</v>
       </c>
@@ -15558,26 +15577,26 @@
       <c r="P158" s="6">
         <v>0</v>
       </c>
-      <c r="Q158" s="10"/>
-      <c r="R158" s="4">
+      <c r="Q158" s="25"/>
+      <c r="R158" s="11">
         <v>1000</v>
       </c>
-      <c r="S158" s="4">
+      <c r="S158" s="11">
         <v>2667</v>
       </c>
-      <c r="T158" s="4">
+      <c r="T158" s="11">
         <v>369.47</v>
       </c>
-      <c r="U158" s="4">
+      <c r="U158" s="11">
         <v>781.27</v>
       </c>
-      <c r="V158" s="4">
+      <c r="V158" s="11">
         <v>40752</v>
       </c>
-      <c r="W158" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y158" s="25"/>
+      <c r="W158" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="15"/>
       <c r="Z158" s="4">
         <v>1000</v>
       </c>
@@ -15601,7 +15620,7 @@
       <c r="B159" t="s">
         <v>39</v>
       </c>
-      <c r="C159" s="9" t="s">
+      <c r="C159" s="21" t="s">
         <v>65</v>
       </c>
       <c r="D159" s="4">
@@ -15622,7 +15641,7 @@
       <c r="I159" s="6">
         <v>0</v>
       </c>
-      <c r="J159" s="9" t="s">
+      <c r="J159" s="21" t="s">
         <v>109</v>
       </c>
       <c r="K159" s="4">
@@ -15643,28 +15662,28 @@
       <c r="P159" s="6">
         <v>0</v>
       </c>
-      <c r="Q159" s="9" t="s">
+      <c r="Q159" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="R159" s="4">
+      <c r="R159" s="11">
         <v>50</v>
       </c>
-      <c r="S159" s="4">
+      <c r="S159" s="11">
         <v>97</v>
       </c>
-      <c r="T159" s="4">
+      <c r="T159" s="11">
         <v>503.18</v>
       </c>
-      <c r="U159" s="4">
+      <c r="U159" s="11">
         <v>525.66999999999996</v>
       </c>
-      <c r="V159" s="4">
+      <c r="V159" s="11">
         <v>1500</v>
       </c>
-      <c r="W159" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y159" s="26" t="s">
+      <c r="W159" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y159" s="14" t="s">
         <v>65</v>
       </c>
       <c r="Z159" s="4">
@@ -15690,7 +15709,7 @@
       <c r="B160" t="s">
         <v>39</v>
       </c>
-      <c r="C160" s="10"/>
+      <c r="C160" s="20"/>
       <c r="D160" s="4">
         <v>100</v>
       </c>
@@ -15709,7 +15728,7 @@
       <c r="I160" s="6">
         <v>0</v>
       </c>
-      <c r="J160" s="10"/>
+      <c r="J160" s="20"/>
       <c r="K160" s="4">
         <v>100</v>
       </c>
@@ -15728,26 +15747,26 @@
       <c r="P160" s="6">
         <v>0</v>
       </c>
-      <c r="Q160" s="10"/>
-      <c r="R160" s="4">
+      <c r="Q160" s="25"/>
+      <c r="R160" s="11">
         <v>100</v>
       </c>
-      <c r="S160" s="4">
+      <c r="S160" s="11">
         <v>194</v>
       </c>
-      <c r="T160" s="4">
+      <c r="T160" s="11">
         <v>503.19</v>
       </c>
-      <c r="U160" s="4">
+      <c r="U160" s="11">
         <v>569.33000000000004</v>
       </c>
-      <c r="V160" s="4">
+      <c r="V160" s="11">
         <v>3000</v>
       </c>
-      <c r="W160" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y160" s="25"/>
+      <c r="W160" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y160" s="15"/>
       <c r="Z160" s="4">
         <v>100</v>
       </c>
@@ -15771,7 +15790,7 @@
       <c r="B161" t="s">
         <v>39</v>
       </c>
-      <c r="C161" s="10"/>
+      <c r="C161" s="20"/>
       <c r="D161" s="4">
         <v>200</v>
       </c>
@@ -15790,7 +15809,7 @@
       <c r="I161" s="6">
         <v>0</v>
       </c>
-      <c r="J161" s="10"/>
+      <c r="J161" s="20"/>
       <c r="K161" s="4">
         <v>200</v>
       </c>
@@ -15809,26 +15828,26 @@
       <c r="P161" s="6">
         <v>0</v>
       </c>
-      <c r="Q161" s="10"/>
-      <c r="R161" s="4">
+      <c r="Q161" s="25"/>
+      <c r="R161" s="11">
         <v>200</v>
       </c>
-      <c r="S161" s="4">
+      <c r="S161" s="11">
         <v>390</v>
       </c>
-      <c r="T161" s="4">
+      <c r="T161" s="11">
         <v>503.98</v>
       </c>
-      <c r="U161" s="4">
+      <c r="U161" s="11">
         <v>583.98</v>
       </c>
-      <c r="V161" s="4">
+      <c r="V161" s="11">
         <v>6000</v>
       </c>
-      <c r="W161" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y161" s="25"/>
+      <c r="W161" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y161" s="15"/>
       <c r="Z161" s="4">
         <v>200</v>
       </c>
@@ -15852,7 +15871,7 @@
       <c r="B162" t="s">
         <v>39</v>
       </c>
-      <c r="C162" s="10"/>
+      <c r="C162" s="20"/>
       <c r="D162" s="4">
         <v>500</v>
       </c>
@@ -15871,7 +15890,7 @@
       <c r="I162" s="6">
         <v>0</v>
       </c>
-      <c r="J162" s="10"/>
+      <c r="J162" s="20"/>
       <c r="K162" s="4">
         <v>500</v>
       </c>
@@ -15890,26 +15909,26 @@
       <c r="P162" s="6">
         <v>0</v>
       </c>
-      <c r="Q162" s="10"/>
-      <c r="R162" s="4">
+      <c r="Q162" s="25"/>
+      <c r="R162" s="11">
         <v>500</v>
       </c>
-      <c r="S162" s="4">
+      <c r="S162" s="11">
         <v>966</v>
       </c>
-      <c r="T162" s="4">
+      <c r="T162" s="11">
         <v>509.39</v>
       </c>
-      <c r="U162" s="4">
+      <c r="U162" s="11">
         <v>737.39</v>
       </c>
-      <c r="V162" s="4">
+      <c r="V162" s="11">
         <v>14883</v>
       </c>
-      <c r="W162" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y162" s="25"/>
+      <c r="W162" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y162" s="15"/>
       <c r="Z162" s="4">
         <v>500</v>
       </c>
@@ -15933,7 +15952,7 @@
       <c r="B163" t="s">
         <v>39</v>
       </c>
-      <c r="C163" s="10"/>
+      <c r="C163" s="20"/>
       <c r="D163" s="4">
         <v>1000</v>
       </c>
@@ -15952,7 +15971,7 @@
       <c r="I163" s="6">
         <v>0</v>
       </c>
-      <c r="J163" s="10"/>
+      <c r="J163" s="20"/>
       <c r="K163" s="4">
         <v>1000</v>
       </c>
@@ -15971,26 +15990,26 @@
       <c r="P163" s="6">
         <v>0</v>
       </c>
-      <c r="Q163" s="10"/>
-      <c r="R163" s="4">
+      <c r="Q163" s="25"/>
+      <c r="R163" s="11">
         <v>1000</v>
       </c>
-      <c r="S163" s="4">
+      <c r="S163" s="11">
         <v>1857</v>
       </c>
-      <c r="T163" s="4">
+      <c r="T163" s="11">
         <v>530.19000000000005</v>
       </c>
-      <c r="U163" s="4">
+      <c r="U163" s="11">
         <v>996.47</v>
       </c>
-      <c r="V163" s="4">
+      <c r="V163" s="11">
         <v>28558</v>
       </c>
-      <c r="W163" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y163" s="25"/>
+      <c r="W163" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y163" s="15"/>
       <c r="Z163" s="4">
         <v>1000</v>
       </c>
@@ -16014,7 +16033,7 @@
       <c r="B164" t="s">
         <v>40</v>
       </c>
-      <c r="C164" s="9" t="s">
+      <c r="C164" s="21" t="s">
         <v>66</v>
       </c>
       <c r="D164" s="4">
@@ -16035,7 +16054,7 @@
       <c r="I164" s="6">
         <v>0</v>
       </c>
-      <c r="J164" s="9" t="s">
+      <c r="J164" s="21" t="s">
         <v>110</v>
       </c>
       <c r="K164" s="4">
@@ -16056,28 +16075,28 @@
       <c r="P164" s="6">
         <v>0</v>
       </c>
-      <c r="Q164" s="9" t="s">
+      <c r="Q164" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="R164" s="4">
+      <c r="R164" s="11">
         <v>50</v>
       </c>
-      <c r="S164" s="4">
+      <c r="S164" s="11">
         <v>47</v>
       </c>
-      <c r="T164" s="4">
+      <c r="T164" s="11">
         <v>1004.63</v>
       </c>
-      <c r="U164" s="4">
+      <c r="U164" s="11">
         <v>1026.3499999999999</v>
       </c>
-      <c r="V164" s="4">
+      <c r="V164" s="11">
         <v>750</v>
       </c>
-      <c r="W164" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y164" s="26" t="s">
+      <c r="W164" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y164" s="14" t="s">
         <v>66</v>
       </c>
       <c r="Z164" s="4">
@@ -16103,7 +16122,7 @@
       <c r="B165" t="s">
         <v>40</v>
       </c>
-      <c r="C165" s="10"/>
+      <c r="C165" s="20"/>
       <c r="D165" s="4">
         <v>100</v>
       </c>
@@ -16122,7 +16141,7 @@
       <c r="I165" s="6">
         <v>0</v>
       </c>
-      <c r="J165" s="10"/>
+      <c r="J165" s="20"/>
       <c r="K165" s="4">
         <v>100</v>
       </c>
@@ -16141,26 +16160,26 @@
       <c r="P165" s="6">
         <v>0</v>
       </c>
-      <c r="Q165" s="10"/>
-      <c r="R165" s="4">
+      <c r="Q165" s="25"/>
+      <c r="R165" s="11">
         <v>100</v>
       </c>
-      <c r="S165" s="4">
+      <c r="S165" s="11">
         <v>95</v>
       </c>
-      <c r="T165" s="4">
+      <c r="T165" s="11">
         <v>1004.61</v>
       </c>
-      <c r="U165" s="4">
+      <c r="U165" s="11">
         <v>1065.3900000000001</v>
       </c>
-      <c r="V165" s="4">
+      <c r="V165" s="11">
         <v>1500</v>
       </c>
-      <c r="W165" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y165" s="25"/>
+      <c r="W165" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="15"/>
       <c r="Z165" s="4">
         <v>100</v>
       </c>
@@ -16184,7 +16203,7 @@
       <c r="B166" t="s">
         <v>40</v>
       </c>
-      <c r="C166" s="11"/>
+      <c r="C166" s="26"/>
       <c r="D166" s="7">
         <v>200</v>
       </c>
@@ -16203,7 +16222,7 @@
       <c r="I166" s="8">
         <v>0</v>
       </c>
-      <c r="J166" s="11"/>
+      <c r="J166" s="26"/>
       <c r="K166" s="7">
         <v>200</v>
       </c>
@@ -16222,26 +16241,26 @@
       <c r="P166" s="8">
         <v>0</v>
       </c>
-      <c r="Q166" s="11"/>
-      <c r="R166" s="7">
+      <c r="Q166" s="31"/>
+      <c r="R166" s="32">
         <v>200</v>
       </c>
-      <c r="S166" s="7">
+      <c r="S166" s="32">
         <v>189</v>
       </c>
-      <c r="T166" s="7">
+      <c r="T166" s="32">
         <v>1005.82</v>
       </c>
-      <c r="U166" s="7">
+      <c r="U166" s="32">
         <v>1068.58</v>
       </c>
-      <c r="V166" s="7">
+      <c r="V166" s="32">
         <v>3000</v>
       </c>
-      <c r="W166" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y166" s="25"/>
+      <c r="W166" s="33">
+        <v>0</v>
+      </c>
+      <c r="Y166" s="15"/>
       <c r="Z166" s="4">
         <v>200</v>
       </c>
@@ -16278,6 +16297,122 @@
     </row>
   </sheetData>
   <mergeCells count="140">
+    <mergeCell ref="Q164:Q166"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="Q134:Q138"/>
+    <mergeCell ref="Q139:Q143"/>
+    <mergeCell ref="Q144:Q148"/>
+    <mergeCell ref="Q149:Q153"/>
+    <mergeCell ref="Q154:Q158"/>
+    <mergeCell ref="Q159:Q163"/>
+    <mergeCell ref="Q108:Q112"/>
+    <mergeCell ref="Q113:Q117"/>
+    <mergeCell ref="Q118:Q122"/>
+    <mergeCell ref="Q123:Q127"/>
+    <mergeCell ref="Q128:Q130"/>
+    <mergeCell ref="Q131:Q133"/>
+    <mergeCell ref="Q78:Q82"/>
+    <mergeCell ref="Q83:Q87"/>
+    <mergeCell ref="Q88:Q92"/>
+    <mergeCell ref="Q93:Q97"/>
+    <mergeCell ref="Q98:Q102"/>
+    <mergeCell ref="Q103:Q107"/>
+    <mergeCell ref="Q48:Q52"/>
+    <mergeCell ref="Q53:Q57"/>
+    <mergeCell ref="Q58:Q62"/>
+    <mergeCell ref="Q63:Q67"/>
+    <mergeCell ref="J88:J92"/>
+    <mergeCell ref="J93:J97"/>
+    <mergeCell ref="J98:J102"/>
+    <mergeCell ref="J103:J107"/>
+    <mergeCell ref="J108:J112"/>
+    <mergeCell ref="J113:J117"/>
+    <mergeCell ref="J58:J62"/>
+    <mergeCell ref="J63:J67"/>
+    <mergeCell ref="J68:J72"/>
+    <mergeCell ref="J73:J77"/>
+    <mergeCell ref="J78:J82"/>
+    <mergeCell ref="J83:J87"/>
+    <mergeCell ref="J149:J153"/>
+    <mergeCell ref="J154:J158"/>
+    <mergeCell ref="J159:J163"/>
+    <mergeCell ref="J164:J166"/>
+    <mergeCell ref="J118:J122"/>
+    <mergeCell ref="J123:J127"/>
+    <mergeCell ref="J128:J130"/>
+    <mergeCell ref="J131:J133"/>
+    <mergeCell ref="J134:J138"/>
+    <mergeCell ref="J139:J143"/>
+    <mergeCell ref="J144:J148"/>
+    <mergeCell ref="C88:C92"/>
+    <mergeCell ref="C93:C97"/>
+    <mergeCell ref="C98:C102"/>
+    <mergeCell ref="C103:C107"/>
+    <mergeCell ref="C108:C112"/>
+    <mergeCell ref="C113:C117"/>
+    <mergeCell ref="C58:C62"/>
+    <mergeCell ref="C63:C67"/>
+    <mergeCell ref="C68:C72"/>
+    <mergeCell ref="C73:C77"/>
+    <mergeCell ref="C139:C143"/>
+    <mergeCell ref="C144:C148"/>
+    <mergeCell ref="C149:C153"/>
+    <mergeCell ref="C154:C158"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="C164:C166"/>
+    <mergeCell ref="C118:C122"/>
+    <mergeCell ref="C123:C127"/>
+    <mergeCell ref="C128:C130"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="C134:C138"/>
+    <mergeCell ref="C23:C27"/>
+    <mergeCell ref="J13:J17"/>
+    <mergeCell ref="J18:J22"/>
+    <mergeCell ref="J23:J27"/>
+    <mergeCell ref="Q13:Q17"/>
+    <mergeCell ref="C78:C82"/>
+    <mergeCell ref="C83:C87"/>
+    <mergeCell ref="C28:C32"/>
+    <mergeCell ref="C33:C37"/>
+    <mergeCell ref="C38:C42"/>
+    <mergeCell ref="C43:C47"/>
+    <mergeCell ref="C48:C52"/>
+    <mergeCell ref="C53:C57"/>
+    <mergeCell ref="J43:J47"/>
+    <mergeCell ref="J48:J52"/>
+    <mergeCell ref="J53:J57"/>
+    <mergeCell ref="Q68:Q72"/>
+    <mergeCell ref="Q73:Q77"/>
+    <mergeCell ref="Q18:Q22"/>
+    <mergeCell ref="Q23:Q27"/>
+    <mergeCell ref="Q28:Q32"/>
+    <mergeCell ref="Q33:Q37"/>
+    <mergeCell ref="Q38:Q42"/>
+    <mergeCell ref="Q43:Q47"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="J3:J7"/>
+    <mergeCell ref="Q3:Q7"/>
+    <mergeCell ref="Y3:Y7"/>
+    <mergeCell ref="Y8:Y12"/>
+    <mergeCell ref="Y13:Y17"/>
+    <mergeCell ref="Y18:Y22"/>
+    <mergeCell ref="J8:J12"/>
+    <mergeCell ref="Q8:Q12"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="C18:C22"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="Y33:Y37"/>
+    <mergeCell ref="Y38:Y42"/>
+    <mergeCell ref="Y43:Y47"/>
+    <mergeCell ref="Y48:Y52"/>
+    <mergeCell ref="Y53:Y57"/>
+    <mergeCell ref="Y58:Y62"/>
+    <mergeCell ref="Y63:Y67"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="J28:J32"/>
+    <mergeCell ref="J33:J37"/>
+    <mergeCell ref="J38:J42"/>
     <mergeCell ref="Y154:Y158"/>
     <mergeCell ref="Y159:Y163"/>
     <mergeCell ref="Y164:Y166"/>
@@ -16302,122 +16437,6 @@
     <mergeCell ref="Y108:Y112"/>
     <mergeCell ref="Y23:Y27"/>
     <mergeCell ref="Y28:Y32"/>
-    <mergeCell ref="Y33:Y37"/>
-    <mergeCell ref="Y38:Y42"/>
-    <mergeCell ref="Y43:Y47"/>
-    <mergeCell ref="Y48:Y52"/>
-    <mergeCell ref="Y53:Y57"/>
-    <mergeCell ref="Y58:Y62"/>
-    <mergeCell ref="Y63:Y67"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="Q1:W1"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="J3:J7"/>
-    <mergeCell ref="Q3:Q7"/>
-    <mergeCell ref="Y3:Y7"/>
-    <mergeCell ref="Y8:Y12"/>
-    <mergeCell ref="Y13:Y17"/>
-    <mergeCell ref="Y18:Y22"/>
-    <mergeCell ref="J8:J12"/>
-    <mergeCell ref="Q8:Q12"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="C18:C22"/>
-    <mergeCell ref="C23:C27"/>
-    <mergeCell ref="J13:J17"/>
-    <mergeCell ref="J18:J22"/>
-    <mergeCell ref="J23:J27"/>
-    <mergeCell ref="Q13:Q17"/>
-    <mergeCell ref="C78:C82"/>
-    <mergeCell ref="C83:C87"/>
-    <mergeCell ref="C28:C32"/>
-    <mergeCell ref="C33:C37"/>
-    <mergeCell ref="C38:C42"/>
-    <mergeCell ref="C43:C47"/>
-    <mergeCell ref="C48:C52"/>
-    <mergeCell ref="C53:C57"/>
-    <mergeCell ref="C8:C12"/>
-    <mergeCell ref="J43:J47"/>
-    <mergeCell ref="J48:J52"/>
-    <mergeCell ref="J53:J57"/>
-    <mergeCell ref="C139:C143"/>
-    <mergeCell ref="C144:C148"/>
-    <mergeCell ref="C149:C153"/>
-    <mergeCell ref="C154:C158"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="C164:C166"/>
-    <mergeCell ref="C118:C122"/>
-    <mergeCell ref="C123:C127"/>
-    <mergeCell ref="C128:C130"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="C134:C138"/>
-    <mergeCell ref="C88:C92"/>
-    <mergeCell ref="C93:C97"/>
-    <mergeCell ref="C98:C102"/>
-    <mergeCell ref="C103:C107"/>
-    <mergeCell ref="C108:C112"/>
-    <mergeCell ref="C113:C117"/>
-    <mergeCell ref="C58:C62"/>
-    <mergeCell ref="C63:C67"/>
-    <mergeCell ref="C68:C72"/>
-    <mergeCell ref="C73:C77"/>
-    <mergeCell ref="J149:J153"/>
-    <mergeCell ref="J154:J158"/>
-    <mergeCell ref="J159:J163"/>
-    <mergeCell ref="J164:J166"/>
-    <mergeCell ref="J118:J122"/>
-    <mergeCell ref="J123:J127"/>
-    <mergeCell ref="J128:J130"/>
-    <mergeCell ref="J131:J133"/>
-    <mergeCell ref="J134:J138"/>
-    <mergeCell ref="J139:J143"/>
-    <mergeCell ref="Q68:Q72"/>
-    <mergeCell ref="Q73:Q77"/>
-    <mergeCell ref="Q18:Q22"/>
-    <mergeCell ref="Q23:Q27"/>
-    <mergeCell ref="Q28:Q32"/>
-    <mergeCell ref="Q33:Q37"/>
-    <mergeCell ref="Q38:Q42"/>
-    <mergeCell ref="Q43:Q47"/>
-    <mergeCell ref="J144:J148"/>
-    <mergeCell ref="J88:J92"/>
-    <mergeCell ref="J93:J97"/>
-    <mergeCell ref="J98:J102"/>
-    <mergeCell ref="J103:J107"/>
-    <mergeCell ref="J108:J112"/>
-    <mergeCell ref="J113:J117"/>
-    <mergeCell ref="J58:J62"/>
-    <mergeCell ref="J63:J67"/>
-    <mergeCell ref="J68:J72"/>
-    <mergeCell ref="J73:J77"/>
-    <mergeCell ref="J78:J82"/>
-    <mergeCell ref="J83:J87"/>
-    <mergeCell ref="J28:J32"/>
-    <mergeCell ref="J33:J37"/>
-    <mergeCell ref="J38:J42"/>
-    <mergeCell ref="Q164:Q166"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="Q134:Q138"/>
-    <mergeCell ref="Q139:Q143"/>
-    <mergeCell ref="Q144:Q148"/>
-    <mergeCell ref="Q149:Q153"/>
-    <mergeCell ref="Q154:Q158"/>
-    <mergeCell ref="Q159:Q163"/>
-    <mergeCell ref="Q108:Q112"/>
-    <mergeCell ref="Q113:Q117"/>
-    <mergeCell ref="Q118:Q122"/>
-    <mergeCell ref="Q123:Q127"/>
-    <mergeCell ref="Q128:Q130"/>
-    <mergeCell ref="Q131:Q133"/>
-    <mergeCell ref="Q78:Q82"/>
-    <mergeCell ref="Q83:Q87"/>
-    <mergeCell ref="Q88:Q92"/>
-    <mergeCell ref="Q93:Q97"/>
-    <mergeCell ref="Q98:Q102"/>
-    <mergeCell ref="Q103:Q107"/>
-    <mergeCell ref="Q48:Q52"/>
-    <mergeCell ref="Q53:Q57"/>
-    <mergeCell ref="Q58:Q62"/>
-    <mergeCell ref="Q63:Q67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
